--- a/no_room_for_heroes/GRAPHICS_ASSET_LIST.xlsx
+++ b/no_room_for_heroes/GRAPHICS_ASSET_LIST.xlsx
@@ -339,12 +339,12 @@
     <row r="10">
       <c r="A10" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">Rooms — trap cells</t>
+          <t xml:space="preserve">Rooms — standard</t>
         </is>
       </c>
       <c r="B10" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="C10" t="inlineStr" s="6">
@@ -354,24 +354,24 @@
       </c>
       <c r="D10" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">15</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="E10" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">12</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">Rooms — monster cells</t>
+          <t xml:space="preserve">Rooms — trap overlays</t>
         </is>
       </c>
       <c r="B11" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
       <c r="C11" t="inlineStr" s="6">
@@ -386,7 +386,7 @@
       </c>
       <c r="E11" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">15</t>
         </is>
       </c>
     </row>
@@ -398,7 +398,7 @@
       </c>
       <c r="B12" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
       <c r="C12" t="inlineStr" s="6">
@@ -408,7 +408,7 @@
       </c>
       <c r="D12" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="E12" t="inlineStr" s="6">
@@ -582,12 +582,12 @@
     <row r="19">
       <c r="A19" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">TOTAL (218 assets)</t>
+          <t xml:space="preserve">TOTAL (196 assets)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">56</t>
+          <t xml:space="preserve">50</t>
         </is>
       </c>
       <c r="C19" t="inlineStr" s="6">
@@ -597,12 +597,12 @@
       </c>
       <c r="D19" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">69</t>
+          <t xml:space="preserve">54</t>
         </is>
       </c>
       <c r="E19" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">89</t>
+          <t xml:space="preserve">88</t>
         </is>
       </c>
     </row>
@@ -5942,22 +5942,22 @@
     <row r="89">
       <c r="A89" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">Rooms — trap cells</t>
+          <t xml:space="preserve">Rooms — standard</t>
         </is>
       </c>
       <c r="B89" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">Spike Pit</t>
+          <t xml:space="preserve">Standard room</t>
         </is>
       </c>
       <c r="C89" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">Room interior art</t>
+          <t xml:space="preserve">Standard room interior (every cell)</t>
         </is>
       </c>
       <c r="D89" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">rooms/spike.png</t>
+          <t xml:space="preserve">rooms/empty.png</t>
         </is>
       </c>
       <c r="E89" t="inlineStr" s="2">
@@ -5977,12 +5977,12 @@
       </c>
       <c r="H89" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">~183x192 (match spike.png), alpha</t>
+          <t xml:space="preserve">~183x192, alpha</t>
         </is>
       </c>
       <c r="I89" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">bottom sits 12px below floor</t>
+          <t xml:space="preserve">bottom 12px below floor</t>
         </is>
       </c>
       <c r="J89" t="inlineStr" s="6">
@@ -5992,91 +5992,91 @@
       </c>
       <c r="K89" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">Live.</t>
+          <t xml:space="preserve">Live. ALL cells use it; contents overlay.</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">Rooms — trap cells</t>
+          <t xml:space="preserve">Rooms — standard</t>
         </is>
       </c>
       <c r="B90" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">Spike Pit</t>
+          <t xml:space="preserve">Standard room</t>
         </is>
       </c>
       <c r="C90" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">Trigger/firing animation</t>
+          <t xml:space="preserve">Broken doorway variant</t>
         </is>
       </c>
       <c r="D90" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">rooms/fx/spike_fire_0..4.png</t>
-        </is>
-      </c>
-      <c r="E90" t="inlineStr" s="5">
-        <is>
-          <t xml:space="preserve">PROCEDURAL</t>
+          <t xml:space="preserve">rooms/empty_broken.png</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr" s="4">
+        <is>
+          <t xml:space="preserve">MISSING</t>
         </is>
       </c>
       <c r="F90" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">animation</t>
+          <t xml:space="preserve">static</t>
         </is>
       </c>
       <c r="G90" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">4-6</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H90" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">~200x150, alpha</t>
+          <t xml:space="preserve">~183x192</t>
         </is>
       </c>
       <c r="I90" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">plays over the room</t>
+          <t xml:space="preserve">left doorway smashed</t>
         </is>
       </c>
       <c r="J90" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">P2</t>
+          <t xml:space="preserve">P1</t>
         </is>
       </c>
       <c r="K90" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">All trap firings are canvas FX today — sprite anims are the big juice upgrade.</t>
+          <t xml:space="preserve">Switches in when a champion crashes through (effects already live).</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">Rooms — trap cells</t>
+          <t xml:space="preserve">Rooms — standard</t>
         </is>
       </c>
       <c r="B91" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">Flame Jet</t>
+          <t xml:space="preserve">Gate</t>
         </is>
       </c>
       <c r="C91" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">Room interior art</t>
+          <t xml:space="preserve">Entrance gate / staging area art</t>
         </is>
       </c>
       <c r="D91" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">rooms/flame.png</t>
-        </is>
-      </c>
-      <c r="E91" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">HAVE</t>
+          <t xml:space="preserve">rooms/gate.png</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr" s="5">
+        <is>
+          <t xml:space="preserve">PROCEDURAL</t>
         </is>
       </c>
       <c r="F91" t="inlineStr" s="6">
@@ -6091,101 +6091,101 @@
       </c>
       <c r="H91" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">~183x192 (match spike.png), alpha</t>
+          <t xml:space="preserve">~150x200</t>
         </is>
       </c>
       <c r="I91" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">bottom sits 12px below floor</t>
+          <t xml:space="preserve">left of room 0</t>
         </is>
       </c>
       <c r="J91" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">P1</t>
+          <t xml:space="preserve">P2</t>
         </is>
       </c>
       <c r="K91" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">Live.</t>
+          <t xml:space="preserve">Heroes march in from outside — a painted gate would sell it.</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">Rooms — trap cells</t>
+          <t xml:space="preserve">Rooms — trap overlays</t>
         </is>
       </c>
       <c r="B92" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">Flame Jet</t>
+          <t xml:space="preserve">Spike Pit</t>
         </is>
       </c>
       <c r="C92" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">Trigger/firing animation</t>
+          <t xml:space="preserve">Trap sprite or animation</t>
         </is>
       </c>
       <c r="D92" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">rooms/fx/flame_fire_0..4.png</t>
-        </is>
-      </c>
-      <c r="E92" t="inlineStr" s="5">
-        <is>
-          <t xml:space="preserve">PROCEDURAL</t>
+          <t xml:space="preserve">rooms/traps/spike.png (static) or spike_0..N.png (anim)</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr" s="4">
+        <is>
+          <t xml:space="preserve">MISSING</t>
         </is>
       </c>
       <c r="F92" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">animation</t>
+          <t xml:space="preserve">static or animation</t>
         </is>
       </c>
       <c r="G92" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">4-6</t>
+          <t xml:space="preserve">1 or 2-12</t>
         </is>
       </c>
       <c r="H92" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">~200x150, alpha</t>
+          <t xml:space="preserve">~256px tall (shows ~100-110px)</t>
         </is>
       </c>
       <c r="I92" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">plays over the room</t>
+          <t xml:space="preserve">centered, feet on floor</t>
         </is>
       </c>
       <c r="J92" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">P2</t>
+          <t xml:space="preserve">P1</t>
         </is>
       </c>
       <c r="K92" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">All trap firings are canvas FX today — sprite anims are the big juice upgrade.</t>
+          <t xml:space="preserve">Loops ~7fps; procedural prop draws until uploaded — upgrade one trap at a time.</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">Rooms — trap cells</t>
+          <t xml:space="preserve">Rooms — trap overlays</t>
         </is>
       </c>
       <c r="B93" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">Dart Wall</t>
+          <t xml:space="preserve">Flame Jet</t>
         </is>
       </c>
       <c r="C93" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">Room interior art</t>
+          <t xml:space="preserve">Trap sprite or animation</t>
         </is>
       </c>
       <c r="D93" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">rooms/arrow.png</t>
+          <t xml:space="preserve">rooms/traps/flame.png (static) or flame_0..N.png (anim)</t>
         </is>
       </c>
       <c r="E93" t="inlineStr" s="4">
@@ -6195,22 +6195,22 @@
       </c>
       <c r="F93" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">static</t>
+          <t xml:space="preserve">static or animation</t>
         </is>
       </c>
       <c r="G93" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">1 or 2-12</t>
         </is>
       </c>
       <c r="H93" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">~183x192 (match spike.png), alpha</t>
+          <t xml:space="preserve">~256px tall (shows ~100-110px)</t>
         </is>
       </c>
       <c r="I93" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">bottom sits 12px below floor</t>
+          <t xml:space="preserve">centered, feet on floor</t>
         </is>
       </c>
       <c r="J93" t="inlineStr" s="6">
@@ -6220,14 +6220,14 @@
       </c>
       <c r="K93" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">Cell renders procedural trap prop today. Match the live spike/flame/oil style.</t>
+          <t xml:space="preserve">Loops ~7fps; procedural prop draws until uploaded — upgrade one trap at a time.</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">Rooms — trap cells</t>
+          <t xml:space="preserve">Rooms — trap overlays</t>
         </is>
       </c>
       <c r="B94" t="inlineStr" s="6">
@@ -6237,54 +6237,54 @@
       </c>
       <c r="C94" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">Trigger/firing animation</t>
+          <t xml:space="preserve">Trap sprite or animation</t>
         </is>
       </c>
       <c r="D94" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">rooms/fx/arrow_fire_0..4.png</t>
-        </is>
-      </c>
-      <c r="E94" t="inlineStr" s="5">
-        <is>
-          <t xml:space="preserve">PROCEDURAL</t>
+          <t xml:space="preserve">rooms/traps/arrow.png (static) or arrow_0..N.png (anim)</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr" s="4">
+        <is>
+          <t xml:space="preserve">MISSING</t>
         </is>
       </c>
       <c r="F94" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">animation</t>
+          <t xml:space="preserve">static or animation</t>
         </is>
       </c>
       <c r="G94" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">4-6</t>
+          <t xml:space="preserve">1 or 2-12</t>
         </is>
       </c>
       <c r="H94" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">~200x150, alpha</t>
+          <t xml:space="preserve">~256px tall (shows ~100-110px)</t>
         </is>
       </c>
       <c r="I94" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">plays over the room</t>
+          <t xml:space="preserve">centered, feet on floor</t>
         </is>
       </c>
       <c r="J94" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">P2</t>
+          <t xml:space="preserve">P1</t>
         </is>
       </c>
       <c r="K94" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">All trap firings are canvas FX today — sprite anims are the big juice upgrade.</t>
+          <t xml:space="preserve">Loops ~7fps; procedural prop draws until uploaded — upgrade one trap at a time.</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">Rooms — trap cells</t>
+          <t xml:space="preserve">Rooms — trap overlays</t>
         </is>
       </c>
       <c r="B95" t="inlineStr" s="6">
@@ -6294,37 +6294,37 @@
       </c>
       <c r="C95" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">Room interior art</t>
+          <t xml:space="preserve">Trap sprite or animation</t>
         </is>
       </c>
       <c r="D95" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">rooms/oil.png</t>
-        </is>
-      </c>
-      <c r="E95" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">HAVE</t>
+          <t xml:space="preserve">rooms/traps/oil.png (static) or oil_0..N.png (anim)</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr" s="4">
+        <is>
+          <t xml:space="preserve">MISSING</t>
         </is>
       </c>
       <c r="F95" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">static</t>
+          <t xml:space="preserve">static or animation</t>
         </is>
       </c>
       <c r="G95" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">1 or 2-12</t>
         </is>
       </c>
       <c r="H95" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">~183x192 (match spike.png), alpha</t>
+          <t xml:space="preserve">~256px tall (shows ~100-110px)</t>
         </is>
       </c>
       <c r="I95" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">bottom sits 12px below floor</t>
+          <t xml:space="preserve">centered, feet on floor</t>
         </is>
       </c>
       <c r="J95" t="inlineStr" s="6">
@@ -6334,86 +6334,86 @@
       </c>
       <c r="K95" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">Live.</t>
+          <t xml:space="preserve">Loops ~7fps; procedural prop draws until uploaded — upgrade one trap at a time.</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">Rooms — trap cells</t>
+          <t xml:space="preserve">Rooms — trap overlays</t>
         </is>
       </c>
       <c r="B96" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">Oil Slick</t>
+          <t xml:space="preserve">Frost Trap</t>
         </is>
       </c>
       <c r="C96" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">Trigger/firing animation</t>
+          <t xml:space="preserve">Trap sprite or animation</t>
         </is>
       </c>
       <c r="D96" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">rooms/fx/oil_fire_0..4.png</t>
-        </is>
-      </c>
-      <c r="E96" t="inlineStr" s="5">
-        <is>
-          <t xml:space="preserve">PROCEDURAL</t>
+          <t xml:space="preserve">rooms/traps/frost.png (static) or frost_0..N.png (anim)</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr" s="4">
+        <is>
+          <t xml:space="preserve">MISSING</t>
         </is>
       </c>
       <c r="F96" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">animation</t>
+          <t xml:space="preserve">static or animation</t>
         </is>
       </c>
       <c r="G96" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">4-6</t>
+          <t xml:space="preserve">1 or 2-12</t>
         </is>
       </c>
       <c r="H96" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">~200x150, alpha</t>
+          <t xml:space="preserve">~256px tall (shows ~100-110px)</t>
         </is>
       </c>
       <c r="I96" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">plays over the room</t>
+          <t xml:space="preserve">centered, feet on floor</t>
         </is>
       </c>
       <c r="J96" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">P2</t>
+          <t xml:space="preserve">P1</t>
         </is>
       </c>
       <c r="K96" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">All trap firings are canvas FX today — sprite anims are the big juice upgrade.</t>
+          <t xml:space="preserve">Loops ~7fps; procedural prop draws until uploaded — upgrade one trap at a time.</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">Rooms — trap cells</t>
+          <t xml:space="preserve">Rooms — trap overlays</t>
         </is>
       </c>
       <c r="B97" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">Frost Trap</t>
+          <t xml:space="preserve">Tesla Coil</t>
         </is>
       </c>
       <c r="C97" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">Room interior art</t>
+          <t xml:space="preserve">Trap sprite or animation</t>
         </is>
       </c>
       <c r="D97" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">rooms/frost.png</t>
+          <t xml:space="preserve">rooms/traps/tesla.png (static) or tesla_0..N.png (anim)</t>
         </is>
       </c>
       <c r="E97" t="inlineStr" s="4">
@@ -6423,22 +6423,22 @@
       </c>
       <c r="F97" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">static</t>
+          <t xml:space="preserve">static or animation</t>
         </is>
       </c>
       <c r="G97" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">1 or 2-12</t>
         </is>
       </c>
       <c r="H97" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">~183x192 (match spike.png), alpha</t>
+          <t xml:space="preserve">~256px tall (shows ~100-110px)</t>
         </is>
       </c>
       <c r="I97" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">bottom sits 12px below floor</t>
+          <t xml:space="preserve">centered, feet on floor</t>
         </is>
       </c>
       <c r="J97" t="inlineStr" s="6">
@@ -6448,86 +6448,86 @@
       </c>
       <c r="K97" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">Cell renders procedural trap prop today. Match the live spike/flame/oil style.</t>
+          <t xml:space="preserve">Loops ~7fps; procedural prop draws until uploaded — upgrade one trap at a time.</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">Rooms — trap cells</t>
+          <t xml:space="preserve">Rooms — trap overlays</t>
         </is>
       </c>
       <c r="B98" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">Frost Trap</t>
+          <t xml:space="preserve">Mage-Bane</t>
         </is>
       </c>
       <c r="C98" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">Trigger/firing animation</t>
+          <t xml:space="preserve">Trap sprite or animation</t>
         </is>
       </c>
       <c r="D98" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">rooms/fx/frost_fire_0..4.png</t>
-        </is>
-      </c>
-      <c r="E98" t="inlineStr" s="5">
-        <is>
-          <t xml:space="preserve">PROCEDURAL</t>
+          <t xml:space="preserve">rooms/traps/magebane.png (static) or magebane_0..N.png (anim)</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr" s="4">
+        <is>
+          <t xml:space="preserve">MISSING</t>
         </is>
       </c>
       <c r="F98" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">animation</t>
+          <t xml:space="preserve">static or animation</t>
         </is>
       </c>
       <c r="G98" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">4-6</t>
+          <t xml:space="preserve">1 or 2-12</t>
         </is>
       </c>
       <c r="H98" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">~200x150, alpha</t>
+          <t xml:space="preserve">~256px tall (shows ~100-110px)</t>
         </is>
       </c>
       <c r="I98" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">plays over the room</t>
+          <t xml:space="preserve">centered, feet on floor</t>
         </is>
       </c>
       <c r="J98" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">P2</t>
+          <t xml:space="preserve">P1</t>
         </is>
       </c>
       <c r="K98" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">All trap firings are canvas FX today — sprite anims are the big juice upgrade.</t>
+          <t xml:space="preserve">Loops ~7fps; procedural prop draws until uploaded — upgrade one trap at a time.</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">Rooms — trap cells</t>
+          <t xml:space="preserve">Rooms — trap overlays</t>
         </is>
       </c>
       <c r="B99" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">Tesla Coil</t>
+          <t xml:space="preserve">Armor Crusher</t>
         </is>
       </c>
       <c r="C99" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">Room interior art</t>
+          <t xml:space="preserve">Trap sprite or animation</t>
         </is>
       </c>
       <c r="D99" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">rooms/tesla.png</t>
+          <t xml:space="preserve">rooms/traps/maul.png (static) or maul_0..N.png (anim)</t>
         </is>
       </c>
       <c r="E99" t="inlineStr" s="4">
@@ -6537,22 +6537,22 @@
       </c>
       <c r="F99" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">static</t>
+          <t xml:space="preserve">static or animation</t>
         </is>
       </c>
       <c r="G99" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">1 or 2-12</t>
         </is>
       </c>
       <c r="H99" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">~183x192 (match spike.png), alpha</t>
+          <t xml:space="preserve">~256px tall (shows ~100-110px)</t>
         </is>
       </c>
       <c r="I99" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">bottom sits 12px below floor</t>
+          <t xml:space="preserve">centered, feet on floor</t>
         </is>
       </c>
       <c r="J99" t="inlineStr" s="6">
@@ -6562,86 +6562,86 @@
       </c>
       <c r="K99" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">Cell renders procedural trap prop today. Match the live spike/flame/oil style.</t>
+          <t xml:space="preserve">Loops ~7fps; procedural prop draws until uploaded — upgrade one trap at a time.</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">Rooms — trap cells</t>
+          <t xml:space="preserve">Rooms — trap overlays</t>
         </is>
       </c>
       <c r="B100" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">Tesla Coil</t>
+          <t xml:space="preserve">Gallows</t>
         </is>
       </c>
       <c r="C100" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">Trigger/firing animation</t>
+          <t xml:space="preserve">Trap sprite or animation</t>
         </is>
       </c>
       <c r="D100" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">rooms/fx/tesla_fire_0..4.png</t>
-        </is>
-      </c>
-      <c r="E100" t="inlineStr" s="5">
-        <is>
-          <t xml:space="preserve">PROCEDURAL</t>
+          <t xml:space="preserve">rooms/traps/gallows.png (static) or gallows_0..N.png (anim)</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr" s="4">
+        <is>
+          <t xml:space="preserve">MISSING</t>
         </is>
       </c>
       <c r="F100" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">animation</t>
+          <t xml:space="preserve">static or animation</t>
         </is>
       </c>
       <c r="G100" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">4-6</t>
+          <t xml:space="preserve">1 or 2-12</t>
         </is>
       </c>
       <c r="H100" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">~200x150, alpha</t>
+          <t xml:space="preserve">~256px tall (shows ~100-110px)</t>
         </is>
       </c>
       <c r="I100" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">plays over the room</t>
+          <t xml:space="preserve">centered, feet on floor</t>
         </is>
       </c>
       <c r="J100" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">P2</t>
+          <t xml:space="preserve">P1</t>
         </is>
       </c>
       <c r="K100" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">All trap firings are canvas FX today — sprite anims are the big juice upgrade.</t>
+          <t xml:space="preserve">Loops ~7fps; procedural prop draws until uploaded — upgrade one trap at a time.</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">Rooms — trap cells</t>
+          <t xml:space="preserve">Rooms — trap overlays</t>
         </is>
       </c>
       <c r="B101" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">Mage-Bane</t>
+          <t xml:space="preserve">Hexward</t>
         </is>
       </c>
       <c r="C101" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">Room interior art</t>
+          <t xml:space="preserve">Trap sprite or animation</t>
         </is>
       </c>
       <c r="D101" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">rooms/magebane.png</t>
+          <t xml:space="preserve">rooms/traps/hexward.png (static) or hexward_0..N.png (anim)</t>
         </is>
       </c>
       <c r="E101" t="inlineStr" s="4">
@@ -6651,22 +6651,22 @@
       </c>
       <c r="F101" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">static</t>
+          <t xml:space="preserve">static or animation</t>
         </is>
       </c>
       <c r="G101" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">1 or 2-12</t>
         </is>
       </c>
       <c r="H101" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">~183x192 (match spike.png), alpha</t>
+          <t xml:space="preserve">~256px tall (shows ~100-110px)</t>
         </is>
       </c>
       <c r="I101" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">bottom sits 12px below floor</t>
+          <t xml:space="preserve">centered, feet on floor</t>
         </is>
       </c>
       <c r="J101" t="inlineStr" s="6">
@@ -6676,86 +6676,86 @@
       </c>
       <c r="K101" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">Cell renders procedural trap prop today. Match the live spike/flame/oil style.</t>
+          <t xml:space="preserve">Loops ~7fps; procedural prop draws until uploaded — upgrade one trap at a time.</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">Rooms — trap cells</t>
+          <t xml:space="preserve">Rooms — trap overlays</t>
         </is>
       </c>
       <c r="B102" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">Mage-Bane</t>
+          <t xml:space="preserve">Bombard</t>
         </is>
       </c>
       <c r="C102" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">Trigger/firing animation</t>
+          <t xml:space="preserve">Trap sprite or animation</t>
         </is>
       </c>
       <c r="D102" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">rooms/fx/magebane_fire_0..4.png</t>
-        </is>
-      </c>
-      <c r="E102" t="inlineStr" s="5">
-        <is>
-          <t xml:space="preserve">PROCEDURAL</t>
+          <t xml:space="preserve">rooms/traps/bombard.png (static) or bombard_0..N.png (anim)</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr" s="4">
+        <is>
+          <t xml:space="preserve">MISSING</t>
         </is>
       </c>
       <c r="F102" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">animation</t>
+          <t xml:space="preserve">static or animation</t>
         </is>
       </c>
       <c r="G102" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">4-6</t>
+          <t xml:space="preserve">1 or 2-12</t>
         </is>
       </c>
       <c r="H102" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">~200x150, alpha</t>
+          <t xml:space="preserve">~256px tall (shows ~100-110px)</t>
         </is>
       </c>
       <c r="I102" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">plays over the room</t>
+          <t xml:space="preserve">centered, feet on floor</t>
         </is>
       </c>
       <c r="J102" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">P2</t>
+          <t xml:space="preserve">P1</t>
         </is>
       </c>
       <c r="K102" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">All trap firings are canvas FX today — sprite anims are the big juice upgrade.</t>
+          <t xml:space="preserve">Loops ~7fps; procedural prop draws until uploaded — upgrade one trap at a time.</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">Rooms — trap cells</t>
+          <t xml:space="preserve">Rooms — trap overlays</t>
         </is>
       </c>
       <c r="B103" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">Armor Crusher</t>
+          <t xml:space="preserve">Venom Vent</t>
         </is>
       </c>
       <c r="C103" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">Room interior art</t>
+          <t xml:space="preserve">Trap sprite or animation</t>
         </is>
       </c>
       <c r="D103" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">rooms/maul.png</t>
+          <t xml:space="preserve">rooms/traps/venom.png (static) or venom_0..N.png (anim)</t>
         </is>
       </c>
       <c r="E103" t="inlineStr" s="4">
@@ -6765,22 +6765,22 @@
       </c>
       <c r="F103" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">static</t>
+          <t xml:space="preserve">static or animation</t>
         </is>
       </c>
       <c r="G103" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">1 or 2-12</t>
         </is>
       </c>
       <c r="H103" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">~183x192 (match spike.png), alpha</t>
+          <t xml:space="preserve">~256px tall (shows ~100-110px)</t>
         </is>
       </c>
       <c r="I103" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">bottom sits 12px below floor</t>
+          <t xml:space="preserve">centered, feet on floor</t>
         </is>
       </c>
       <c r="J103" t="inlineStr" s="6">
@@ -6790,86 +6790,86 @@
       </c>
       <c r="K103" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">Cell renders procedural trap prop today. Match the live spike/flame/oil style.</t>
+          <t xml:space="preserve">Loops ~7fps; procedural prop draws until uploaded — upgrade one trap at a time.</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">Rooms — trap cells</t>
+          <t xml:space="preserve">Rooms — trap overlays</t>
         </is>
       </c>
       <c r="B104" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">Armor Crusher</t>
+          <t xml:space="preserve">Acid Sprayer</t>
         </is>
       </c>
       <c r="C104" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">Trigger/firing animation</t>
+          <t xml:space="preserve">Trap sprite or animation</t>
         </is>
       </c>
       <c r="D104" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">rooms/fx/maul_fire_0..4.png</t>
-        </is>
-      </c>
-      <c r="E104" t="inlineStr" s="5">
-        <is>
-          <t xml:space="preserve">PROCEDURAL</t>
+          <t xml:space="preserve">rooms/traps/corrode.png (static) or corrode_0..N.png (anim)</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr" s="4">
+        <is>
+          <t xml:space="preserve">MISSING</t>
         </is>
       </c>
       <c r="F104" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">animation</t>
+          <t xml:space="preserve">static or animation</t>
         </is>
       </c>
       <c r="G104" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">4-6</t>
+          <t xml:space="preserve">1 or 2-12</t>
         </is>
       </c>
       <c r="H104" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">~200x150, alpha</t>
+          <t xml:space="preserve">~256px tall (shows ~100-110px)</t>
         </is>
       </c>
       <c r="I104" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">plays over the room</t>
+          <t xml:space="preserve">centered, feet on floor</t>
         </is>
       </c>
       <c r="J104" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">P2</t>
+          <t xml:space="preserve">P1</t>
         </is>
       </c>
       <c r="K104" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">All trap firings are canvas FX today — sprite anims are the big juice upgrade.</t>
+          <t xml:space="preserve">Loops ~7fps; procedural prop draws until uploaded — upgrade one trap at a time.</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">Rooms — trap cells</t>
+          <t xml:space="preserve">Rooms — trap overlays</t>
         </is>
       </c>
       <c r="B105" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">Gallows</t>
+          <t xml:space="preserve">Hex Brand</t>
         </is>
       </c>
       <c r="C105" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">Room interior art</t>
+          <t xml:space="preserve">Trap sprite or animation</t>
         </is>
       </c>
       <c r="D105" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">rooms/gallows.png</t>
+          <t xml:space="preserve">rooms/traps/hexbrand.png (static) or hexbrand_0..N.png (anim)</t>
         </is>
       </c>
       <c r="E105" t="inlineStr" s="4">
@@ -6879,22 +6879,22 @@
       </c>
       <c r="F105" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">static</t>
+          <t xml:space="preserve">static or animation</t>
         </is>
       </c>
       <c r="G105" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">1 or 2-12</t>
         </is>
       </c>
       <c r="H105" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">~183x192 (match spike.png), alpha</t>
+          <t xml:space="preserve">~256px tall (shows ~100-110px)</t>
         </is>
       </c>
       <c r="I105" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">bottom sits 12px below floor</t>
+          <t xml:space="preserve">centered, feet on floor</t>
         </is>
       </c>
       <c r="J105" t="inlineStr" s="6">
@@ -6904,91 +6904,91 @@
       </c>
       <c r="K105" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">Cell renders procedural trap prop today. Match the live spike/flame/oil style.</t>
+          <t xml:space="preserve">Loops ~7fps; procedural prop draws until uploaded — upgrade one trap at a time.</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">Rooms — trap cells</t>
+          <t xml:space="preserve">Rooms — trap overlays</t>
         </is>
       </c>
       <c r="B106" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">Gallows</t>
+          <t xml:space="preserve">Runestone</t>
         </is>
       </c>
       <c r="C106" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">Trigger/firing animation</t>
+          <t xml:space="preserve">Trap sprite or animation</t>
         </is>
       </c>
       <c r="D106" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">rooms/fx/gallows_fire_0..4.png</t>
-        </is>
-      </c>
-      <c r="E106" t="inlineStr" s="5">
-        <is>
-          <t xml:space="preserve">PROCEDURAL</t>
+          <t xml:space="preserve">rooms/traps/runestone.png (static) or runestone_0..N.png (anim)</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr" s="4">
+        <is>
+          <t xml:space="preserve">MISSING</t>
         </is>
       </c>
       <c r="F106" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">animation</t>
+          <t xml:space="preserve">static or animation</t>
         </is>
       </c>
       <c r="G106" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">4-6</t>
+          <t xml:space="preserve">1 or 2-12</t>
         </is>
       </c>
       <c r="H106" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">~200x150, alpha</t>
+          <t xml:space="preserve">~256px tall (shows ~100-110px)</t>
         </is>
       </c>
       <c r="I106" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">plays over the room</t>
+          <t xml:space="preserve">centered, feet on floor</t>
         </is>
       </c>
       <c r="J106" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">P2</t>
+          <t xml:space="preserve">P1</t>
         </is>
       </c>
       <c r="K106" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">All trap firings are canvas FX today — sprite anims are the big juice upgrade.</t>
+          <t xml:space="preserve">Loops ~7fps; procedural prop draws until uploaded — upgrade one trap at a time.</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">Rooms — trap cells</t>
+          <t xml:space="preserve">Rooms — special</t>
         </is>
       </c>
       <c r="B107" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">Hexward</t>
+          <t xml:space="preserve">Shop</t>
         </is>
       </c>
       <c r="C107" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">Room interior art</t>
+          <t xml:space="preserve">Shop stall overlay + stock items</t>
         </is>
       </c>
       <c r="D107" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">rooms/hexward.png</t>
-        </is>
-      </c>
-      <c r="E107" t="inlineStr" s="4">
-        <is>
-          <t xml:space="preserve">MISSING</t>
+          <t xml:space="preserve">rooms/traps/shop.png (or procedural)</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr" s="5">
+        <is>
+          <t xml:space="preserve">PROCEDURAL</t>
         </is>
       </c>
       <c r="F107" t="inlineStr" s="6">
@@ -6998,49 +6998,49 @@
       </c>
       <c r="G107" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">1+3</t>
         </is>
       </c>
       <c r="H107" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">~183x192 (match spike.png), alpha</t>
+          <t xml:space="preserve">~256px tall</t>
         </is>
       </c>
       <c r="I107" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">bottom sits 12px below floor</t>
+          <t xml:space="preserve">centered</t>
         </is>
       </c>
       <c r="J107" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">P1</t>
+          <t xml:space="preserve">P2</t>
         </is>
       </c>
       <c r="K107" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">Cell renders procedural trap prop today. Match the live spike/flame/oil style.</t>
+          <t xml:space="preserve">Shop draws a procedural stall+stock today.</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">Rooms — trap cells</t>
+          <t xml:space="preserve">Rooms — decals</t>
         </is>
       </c>
       <c r="B108" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">Hexward</t>
+          <t xml:space="preserve">Carnage</t>
         </is>
       </c>
       <c r="C108" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">Trigger/firing animation</t>
+          <t xml:space="preserve">Blood pools / bones / skulls (kill decals)</t>
         </is>
       </c>
       <c r="D108" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">rooms/fx/hexward_fire_0..4.png</t>
+          <t xml:space="preserve">rooms/fx/carnage_*.png</t>
         </is>
       </c>
       <c r="E108" t="inlineStr" s="5">
@@ -7050,59 +7050,59 @@
       </c>
       <c r="F108" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">animation</t>
+          <t xml:space="preserve">static</t>
         </is>
       </c>
       <c r="G108" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">4-6</t>
+          <t xml:space="preserve">6-8 variants</t>
         </is>
       </c>
       <c r="H108" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">~200x150, alpha</t>
+          <t xml:space="preserve">24-64 px, alpha</t>
         </is>
       </c>
       <c r="I108" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">plays over the room</t>
+          <t xml:space="preserve">floor decals</t>
         </is>
       </c>
       <c r="J108" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">P2</t>
+          <t xml:space="preserve">P3</t>
         </is>
       </c>
       <c r="K108" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">All trap firings are canvas FX today — sprite anims are the big juice upgrade.</t>
+          <t xml:space="preserve">Procedural deterministic decals today.</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">Rooms — trap cells</t>
+          <t xml:space="preserve">Card icons</t>
         </is>
       </c>
       <c r="B109" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">Bombard</t>
+          <t xml:space="preserve">Spike Pit</t>
         </is>
       </c>
       <c r="C109" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">Room interior art</t>
+          <t xml:space="preserve">Hand-card face icon</t>
         </is>
       </c>
       <c r="D109" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">rooms/bombard.png</t>
-        </is>
-      </c>
-      <c r="E109" t="inlineStr" s="4">
-        <is>
-          <t xml:space="preserve">MISSING</t>
+          <t xml:space="preserve">icons/spike.png</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">HAVE</t>
         </is>
       </c>
       <c r="F109" t="inlineStr" s="6">
@@ -7117,69 +7117,69 @@
       </c>
       <c r="H109" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">~183x192 (match spike.png), alpha</t>
+          <t xml:space="preserve">128x128 (shows at 50px)</t>
         </is>
       </c>
       <c r="I109" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">bottom sits 12px below floor</t>
+          <t xml:space="preserve">centered, alpha</t>
         </is>
       </c>
       <c r="J109" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">P1</t>
+          <t xml:space="preserve">P2</t>
         </is>
       </c>
       <c r="K109" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">Cell renders procedural trap prop today. Match the live spike/flame/oil style.</t>
+          <t xml:space="preserve">Live.</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">Rooms — trap cells</t>
+          <t xml:space="preserve">Card icons</t>
         </is>
       </c>
       <c r="B110" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">Bombard</t>
+          <t xml:space="preserve">Flame Jet</t>
         </is>
       </c>
       <c r="C110" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">Trigger/firing animation</t>
+          <t xml:space="preserve">Hand-card face icon</t>
         </is>
       </c>
       <c r="D110" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">rooms/fx/bombard_fire_0..4.png</t>
-        </is>
-      </c>
-      <c r="E110" t="inlineStr" s="5">
-        <is>
-          <t xml:space="preserve">PROCEDURAL</t>
+          <t xml:space="preserve">icons/flame.png</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">HAVE</t>
         </is>
       </c>
       <c r="F110" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">animation</t>
+          <t xml:space="preserve">static</t>
         </is>
       </c>
       <c r="G110" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">4-6</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H110" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">~200x150, alpha</t>
+          <t xml:space="preserve">128x128 (shows at 50px)</t>
         </is>
       </c>
       <c r="I110" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">plays over the room</t>
+          <t xml:space="preserve">centered, alpha</t>
         </is>
       </c>
       <c r="J110" t="inlineStr" s="6">
@@ -7189,34 +7189,34 @@
       </c>
       <c r="K110" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">All trap firings are canvas FX today — sprite anims are the big juice upgrade.</t>
+          <t xml:space="preserve">Live.</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">Rooms — trap cells</t>
+          <t xml:space="preserve">Card icons</t>
         </is>
       </c>
       <c r="B111" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">Venom Vent</t>
+          <t xml:space="preserve">Dart Wall</t>
         </is>
       </c>
       <c r="C111" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">Room interior art</t>
+          <t xml:space="preserve">Hand-card face icon</t>
         </is>
       </c>
       <c r="D111" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">rooms/venom.png</t>
-        </is>
-      </c>
-      <c r="E111" t="inlineStr" s="4">
-        <is>
-          <t xml:space="preserve">MISSING</t>
+          <t xml:space="preserve">icons/arrow.png</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">HAVE</t>
         </is>
       </c>
       <c r="F111" t="inlineStr" s="6">
@@ -7231,69 +7231,69 @@
       </c>
       <c r="H111" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">~183x192 (match spike.png), alpha</t>
+          <t xml:space="preserve">128x128 (shows at 50px)</t>
         </is>
       </c>
       <c r="I111" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">bottom sits 12px below floor</t>
+          <t xml:space="preserve">centered, alpha</t>
         </is>
       </c>
       <c r="J111" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">P1</t>
+          <t xml:space="preserve">P2</t>
         </is>
       </c>
       <c r="K111" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">Cell renders procedural trap prop today. Match the live spike/flame/oil style.</t>
+          <t xml:space="preserve">Live.</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">Rooms — trap cells</t>
+          <t xml:space="preserve">Card icons</t>
         </is>
       </c>
       <c r="B112" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">Venom Vent</t>
+          <t xml:space="preserve">Oil Slick</t>
         </is>
       </c>
       <c r="C112" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">Trigger/firing animation</t>
+          <t xml:space="preserve">Hand-card face icon</t>
         </is>
       </c>
       <c r="D112" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">rooms/fx/venom_fire_0..4.png</t>
-        </is>
-      </c>
-      <c r="E112" t="inlineStr" s="5">
-        <is>
-          <t xml:space="preserve">PROCEDURAL</t>
+          <t xml:space="preserve">icons/oil.png</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">HAVE</t>
         </is>
       </c>
       <c r="F112" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">animation</t>
+          <t xml:space="preserve">static</t>
         </is>
       </c>
       <c r="G112" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">4-6</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H112" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">~200x150, alpha</t>
+          <t xml:space="preserve">128x128 (shows at 50px)</t>
         </is>
       </c>
       <c r="I112" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">plays over the room</t>
+          <t xml:space="preserve">centered, alpha</t>
         </is>
       </c>
       <c r="J112" t="inlineStr" s="6">
@@ -7303,34 +7303,34 @@
       </c>
       <c r="K112" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">All trap firings are canvas FX today — sprite anims are the big juice upgrade.</t>
+          <t xml:space="preserve">Live.</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">Rooms — trap cells</t>
+          <t xml:space="preserve">Card icons</t>
         </is>
       </c>
       <c r="B113" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">Acid Sprayer</t>
+          <t xml:space="preserve">Frost Trap</t>
         </is>
       </c>
       <c r="C113" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">Room interior art</t>
+          <t xml:space="preserve">Hand-card face icon</t>
         </is>
       </c>
       <c r="D113" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">rooms/corrode.png</t>
-        </is>
-      </c>
-      <c r="E113" t="inlineStr" s="4">
-        <is>
-          <t xml:space="preserve">MISSING</t>
+          <t xml:space="preserve">icons/frost.png</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">HAVE</t>
         </is>
       </c>
       <c r="F113" t="inlineStr" s="6">
@@ -7345,69 +7345,69 @@
       </c>
       <c r="H113" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">~183x192 (match spike.png), alpha</t>
+          <t xml:space="preserve">128x128 (shows at 50px)</t>
         </is>
       </c>
       <c r="I113" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">bottom sits 12px below floor</t>
+          <t xml:space="preserve">centered, alpha</t>
         </is>
       </c>
       <c r="J113" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">P1</t>
+          <t xml:space="preserve">P2</t>
         </is>
       </c>
       <c r="K113" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">Cell renders procedural trap prop today. Match the live spike/flame/oil style.</t>
+          <t xml:space="preserve">Live.</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">Rooms — trap cells</t>
+          <t xml:space="preserve">Card icons</t>
         </is>
       </c>
       <c r="B114" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">Acid Sprayer</t>
+          <t xml:space="preserve">Tesla Coil</t>
         </is>
       </c>
       <c r="C114" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">Trigger/firing animation</t>
+          <t xml:space="preserve">Hand-card face icon</t>
         </is>
       </c>
       <c r="D114" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">rooms/fx/corrode_fire_0..4.png</t>
-        </is>
-      </c>
-      <c r="E114" t="inlineStr" s="5">
-        <is>
-          <t xml:space="preserve">PROCEDURAL</t>
+          <t xml:space="preserve">icons/tesla.png</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">HAVE</t>
         </is>
       </c>
       <c r="F114" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">animation</t>
+          <t xml:space="preserve">static</t>
         </is>
       </c>
       <c r="G114" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">4-6</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H114" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">~200x150, alpha</t>
+          <t xml:space="preserve">128x128 (shows at 50px)</t>
         </is>
       </c>
       <c r="I114" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">plays over the room</t>
+          <t xml:space="preserve">centered, alpha</t>
         </is>
       </c>
       <c r="J114" t="inlineStr" s="6">
@@ -7417,34 +7417,34 @@
       </c>
       <c r="K114" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">All trap firings are canvas FX today — sprite anims are the big juice upgrade.</t>
+          <t xml:space="preserve">Live.</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">Rooms — trap cells</t>
+          <t xml:space="preserve">Card icons</t>
         </is>
       </c>
       <c r="B115" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">Hex Brand</t>
+          <t xml:space="preserve">Mage-Bane</t>
         </is>
       </c>
       <c r="C115" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">Room interior art</t>
+          <t xml:space="preserve">Hand-card face icon</t>
         </is>
       </c>
       <c r="D115" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">rooms/hexbrand.png</t>
-        </is>
-      </c>
-      <c r="E115" t="inlineStr" s="4">
-        <is>
-          <t xml:space="preserve">MISSING</t>
+          <t xml:space="preserve">icons/magebane.png</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">HAVE</t>
         </is>
       </c>
       <c r="F115" t="inlineStr" s="6">
@@ -7459,69 +7459,69 @@
       </c>
       <c r="H115" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">~183x192 (match spike.png), alpha</t>
+          <t xml:space="preserve">128x128 (shows at 50px)</t>
         </is>
       </c>
       <c r="I115" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">bottom sits 12px below floor</t>
+          <t xml:space="preserve">centered, alpha</t>
         </is>
       </c>
       <c r="J115" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">P1</t>
+          <t xml:space="preserve">P2</t>
         </is>
       </c>
       <c r="K115" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">Cell renders procedural trap prop today. Match the live spike/flame/oil style.</t>
+          <t xml:space="preserve">Live.</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">Rooms — trap cells</t>
+          <t xml:space="preserve">Card icons</t>
         </is>
       </c>
       <c r="B116" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">Hex Brand</t>
+          <t xml:space="preserve">Armor Crusher</t>
         </is>
       </c>
       <c r="C116" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">Trigger/firing animation</t>
+          <t xml:space="preserve">Hand-card face icon</t>
         </is>
       </c>
       <c r="D116" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">rooms/fx/hexbrand_fire_0..4.png</t>
-        </is>
-      </c>
-      <c r="E116" t="inlineStr" s="5">
-        <is>
-          <t xml:space="preserve">PROCEDURAL</t>
+          <t xml:space="preserve">icons/maul.png</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">HAVE</t>
         </is>
       </c>
       <c r="F116" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">animation</t>
+          <t xml:space="preserve">static</t>
         </is>
       </c>
       <c r="G116" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">4-6</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H116" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">~200x150, alpha</t>
+          <t xml:space="preserve">128x128 (shows at 50px)</t>
         </is>
       </c>
       <c r="I116" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">plays over the room</t>
+          <t xml:space="preserve">centered, alpha</t>
         </is>
       </c>
       <c r="J116" t="inlineStr" s="6">
@@ -7531,34 +7531,34 @@
       </c>
       <c r="K116" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">All trap firings are canvas FX today — sprite anims are the big juice upgrade.</t>
+          <t xml:space="preserve">Live.</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">Rooms — trap cells</t>
+          <t xml:space="preserve">Card icons</t>
         </is>
       </c>
       <c r="B117" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">Runestone</t>
+          <t xml:space="preserve">Gallows</t>
         </is>
       </c>
       <c r="C117" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">Room interior art</t>
+          <t xml:space="preserve">Hand-card face icon</t>
         </is>
       </c>
       <c r="D117" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">rooms/runestone.png</t>
-        </is>
-      </c>
-      <c r="E117" t="inlineStr" s="4">
-        <is>
-          <t xml:space="preserve">MISSING</t>
+          <t xml:space="preserve">icons/gallows.png</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">HAVE</t>
         </is>
       </c>
       <c r="F117" t="inlineStr" s="6">
@@ -7573,69 +7573,69 @@
       </c>
       <c r="H117" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">~183x192 (match spike.png), alpha</t>
+          <t xml:space="preserve">128x128 (shows at 50px)</t>
         </is>
       </c>
       <c r="I117" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">bottom sits 12px below floor</t>
+          <t xml:space="preserve">centered, alpha</t>
         </is>
       </c>
       <c r="J117" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">P1</t>
+          <t xml:space="preserve">P2</t>
         </is>
       </c>
       <c r="K117" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">Cell renders procedural trap prop today. Match the live spike/flame/oil style.</t>
+          <t xml:space="preserve">Live.</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">Rooms — trap cells</t>
+          <t xml:space="preserve">Card icons</t>
         </is>
       </c>
       <c r="B118" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">Runestone</t>
+          <t xml:space="preserve">Hexward</t>
         </is>
       </c>
       <c r="C118" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">Trigger/firing animation</t>
+          <t xml:space="preserve">Hand-card face icon</t>
         </is>
       </c>
       <c r="D118" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">rooms/fx/runestone_fire_0..4.png</t>
-        </is>
-      </c>
-      <c r="E118" t="inlineStr" s="5">
-        <is>
-          <t xml:space="preserve">PROCEDURAL</t>
+          <t xml:space="preserve">icons/hexward.png</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">HAVE</t>
         </is>
       </c>
       <c r="F118" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">animation</t>
+          <t xml:space="preserve">static</t>
         </is>
       </c>
       <c r="G118" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">4-6</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H118" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">~200x150, alpha</t>
+          <t xml:space="preserve">128x128 (shows at 50px)</t>
         </is>
       </c>
       <c r="I118" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">plays over the room</t>
+          <t xml:space="preserve">centered, alpha</t>
         </is>
       </c>
       <c r="J118" t="inlineStr" s="6">
@@ -7645,29 +7645,29 @@
       </c>
       <c r="K118" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">All trap firings are canvas FX today — sprite anims are the big juice upgrade.</t>
+          <t xml:space="preserve">Live.</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">Rooms — monster cells</t>
+          <t xml:space="preserve">Card icons</t>
         </is>
       </c>
       <c r="B119" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">Generic monster lair (Goblin/Ogre use it)</t>
+          <t xml:space="preserve">Bombard</t>
         </is>
       </c>
       <c r="C119" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">Room interior art</t>
+          <t xml:space="preserve">Hand-card face icon</t>
         </is>
       </c>
       <c r="D119" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">rooms/lair.png</t>
+          <t xml:space="preserve">icons/bombard.png</t>
         </is>
       </c>
       <c r="E119" t="inlineStr" s="2">
@@ -7687,12 +7687,12 @@
       </c>
       <c r="H119" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">~183x192</t>
+          <t xml:space="preserve">128x128 (shows at 50px)</t>
         </is>
       </c>
       <c r="I119" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">bottom-aligned</t>
+          <t xml:space="preserve">centered, alpha</t>
         </is>
       </c>
       <c r="J119" t="inlineStr" s="6">
@@ -7709,27 +7709,27 @@
     <row r="120">
       <c r="A120" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">Rooms — monster cells</t>
+          <t xml:space="preserve">Card icons</t>
         </is>
       </c>
       <c r="B120" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">Bone Pit interior</t>
+          <t xml:space="preserve">Venom Vent</t>
         </is>
       </c>
       <c r="C120" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">Room interior art</t>
+          <t xml:space="preserve">Hand-card face icon</t>
         </is>
       </c>
       <c r="D120" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">rooms/skeleton.png</t>
-        </is>
-      </c>
-      <c r="E120" t="inlineStr" s="4">
-        <is>
-          <t xml:space="preserve">MISSING</t>
+          <t xml:space="preserve">icons/venom.png</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">HAVE</t>
         </is>
       </c>
       <c r="F120" t="inlineStr" s="6">
@@ -7744,12 +7744,12 @@
       </c>
       <c r="H120" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">~183x192</t>
+          <t xml:space="preserve">128x128 (shows at 50px)</t>
         </is>
       </c>
       <c r="I120" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">bottom-aligned</t>
+          <t xml:space="preserve">centered, alpha</t>
         </is>
       </c>
       <c r="J120" t="inlineStr" s="6">
@@ -7759,34 +7759,34 @@
       </c>
       <c r="K120" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">Falls back to lair/procedural.</t>
+          <t xml:space="preserve">Live.</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">Rooms — monster cells</t>
+          <t xml:space="preserve">Card icons</t>
         </is>
       </c>
       <c r="B121" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">Warden post interior</t>
+          <t xml:space="preserve">Acid Sprayer</t>
         </is>
       </c>
       <c r="C121" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">Room interior art</t>
+          <t xml:space="preserve">Hand-card face icon</t>
         </is>
       </c>
       <c r="D121" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">rooms/warden.png</t>
-        </is>
-      </c>
-      <c r="E121" t="inlineStr" s="4">
-        <is>
-          <t xml:space="preserve">MISSING</t>
+          <t xml:space="preserve">icons/corrode.png</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">HAVE</t>
         </is>
       </c>
       <c r="F121" t="inlineStr" s="6">
@@ -7801,12 +7801,12 @@
       </c>
       <c r="H121" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">~183x192</t>
+          <t xml:space="preserve">128x128 (shows at 50px)</t>
         </is>
       </c>
       <c r="I121" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">bottom-aligned</t>
+          <t xml:space="preserve">centered, alpha</t>
         </is>
       </c>
       <c r="J121" t="inlineStr" s="6">
@@ -7816,34 +7816,34 @@
       </c>
       <c r="K121" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">Falls back to lair/procedural.</t>
+          <t xml:space="preserve">Live.</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">Rooms — monster cells</t>
+          <t xml:space="preserve">Card icons</t>
         </is>
       </c>
       <c r="B122" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">War Totem interior</t>
+          <t xml:space="preserve">Hex Brand</t>
         </is>
       </c>
       <c r="C122" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">Room interior art</t>
+          <t xml:space="preserve">Hand-card face icon</t>
         </is>
       </c>
       <c r="D122" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">rooms/totem.png</t>
-        </is>
-      </c>
-      <c r="E122" t="inlineStr" s="4">
-        <is>
-          <t xml:space="preserve">MISSING</t>
+          <t xml:space="preserve">icons/hexbrand.png</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">HAVE</t>
         </is>
       </c>
       <c r="F122" t="inlineStr" s="6">
@@ -7858,12 +7858,12 @@
       </c>
       <c r="H122" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">~183x192</t>
+          <t xml:space="preserve">128x128 (shows at 50px)</t>
         </is>
       </c>
       <c r="I122" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">bottom-aligned</t>
+          <t xml:space="preserve">centered, alpha</t>
         </is>
       </c>
       <c r="J122" t="inlineStr" s="6">
@@ -7873,29 +7873,29 @@
       </c>
       <c r="K122" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">Falls back to lair/procedural.</t>
+          <t xml:space="preserve">Live.</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">Rooms — monster cells</t>
+          <t xml:space="preserve">Card icons</t>
         </is>
       </c>
       <c r="B123" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">War Camp interior</t>
+          <t xml:space="preserve">Runestone</t>
         </is>
       </c>
       <c r="C123" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">Room interior art</t>
+          <t xml:space="preserve">Hand-card face icon</t>
         </is>
       </c>
       <c r="D123" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">rooms/warcamp.png</t>
+          <t xml:space="preserve">icons/runestone.png</t>
         </is>
       </c>
       <c r="E123" t="inlineStr" s="4">
@@ -7915,49 +7915,49 @@
       </c>
       <c r="H123" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">~183x192</t>
+          <t xml:space="preserve">128x128 (shows at 50px)</t>
         </is>
       </c>
       <c r="I123" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">bottom-aligned</t>
+          <t xml:space="preserve">centered, alpha</t>
         </is>
       </c>
       <c r="J123" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">P2</t>
+          <t xml:space="preserve">P1</t>
         </is>
       </c>
       <c r="K123" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">Falls back to lair/procedural.</t>
+          <t xml:space="preserve">Card shows emoji today — runestone, warcamp, shop &amp; minion are the only gaps.</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">Rooms — monster cells</t>
+          <t xml:space="preserve">Card icons</t>
         </is>
       </c>
       <c r="B124" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">Gel vat interior</t>
+          <t xml:space="preserve">Goblin Den</t>
         </is>
       </c>
       <c r="C124" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">Room interior art</t>
+          <t xml:space="preserve">Hand-card face icon</t>
         </is>
       </c>
       <c r="D124" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">rooms/slime.png</t>
-        </is>
-      </c>
-      <c r="E124" t="inlineStr" s="4">
-        <is>
-          <t xml:space="preserve">MISSING</t>
+          <t xml:space="preserve">icons/goblin.png</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">HAVE</t>
         </is>
       </c>
       <c r="F124" t="inlineStr" s="6">
@@ -7972,12 +7972,12 @@
       </c>
       <c r="H124" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">~183x192</t>
+          <t xml:space="preserve">128x128 (shows at 50px)</t>
         </is>
       </c>
       <c r="I124" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">bottom-aligned</t>
+          <t xml:space="preserve">centered, alpha</t>
         </is>
       </c>
       <c r="J124" t="inlineStr" s="6">
@@ -7987,29 +7987,29 @@
       </c>
       <c r="K124" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">Falls back to lair/procedural.</t>
+          <t xml:space="preserve">Live.</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">Rooms — special</t>
+          <t xml:space="preserve">Card icons</t>
         </is>
       </c>
       <c r="B125" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">Shop</t>
+          <t xml:space="preserve">Bone Pit</t>
         </is>
       </c>
       <c r="C125" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">Shop interior</t>
+          <t xml:space="preserve">Hand-card face icon</t>
         </is>
       </c>
       <c r="D125" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">rooms/shop.png</t>
+          <t xml:space="preserve">icons/skeleton.png</t>
         </is>
       </c>
       <c r="E125" t="inlineStr" s="2">
@@ -8029,49 +8029,49 @@
       </c>
       <c r="H125" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">~183x192</t>
+          <t xml:space="preserve">128x128 (shows at 50px)</t>
         </is>
       </c>
       <c r="I125" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">—</t>
+          <t xml:space="preserve">centered, alpha</t>
         </is>
       </c>
       <c r="J125" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">P1</t>
+          <t xml:space="preserve">P2</t>
         </is>
       </c>
       <c r="K125" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">Live. Stock items drawn on top procedurally.</t>
+          <t xml:space="preserve">Live.</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">Rooms — special</t>
+          <t xml:space="preserve">Card icons</t>
         </is>
       </c>
       <c r="B126" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">Shop</t>
+          <t xml:space="preserve">Warden</t>
         </is>
       </c>
       <c r="C126" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">Shop stock item icons (weapon/armor/potion)</t>
+          <t xml:space="preserve">Hand-card face icon</t>
         </is>
       </c>
       <c r="D126" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">rooms/fx/stock_*.png</t>
-        </is>
-      </c>
-      <c r="E126" t="inlineStr" s="5">
-        <is>
-          <t xml:space="preserve">PROCEDURAL</t>
+          <t xml:space="preserve">icons/warden.png</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">HAVE</t>
         </is>
       </c>
       <c r="F126" t="inlineStr" s="6">
@@ -8081,49 +8081,49 @@
       </c>
       <c r="G126" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H126" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">32-48 px</t>
+          <t xml:space="preserve">128x128 (shows at 50px)</t>
         </is>
       </c>
       <c r="I126" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">shelf row</t>
+          <t xml:space="preserve">centered, alpha</t>
         </is>
       </c>
       <c r="J126" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">P3</t>
+          <t xml:space="preserve">P2</t>
         </is>
       </c>
       <c r="K126" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">Procedural today.</t>
+          <t xml:space="preserve">Live.</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">Rooms — special</t>
+          <t xml:space="preserve">Card icons</t>
         </is>
       </c>
       <c r="B127" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">Empty slot</t>
+          <t xml:space="preserve">War Totem</t>
         </is>
       </c>
       <c r="C127" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">Empty buildable cell</t>
+          <t xml:space="preserve">Hand-card face icon</t>
         </is>
       </c>
       <c r="D127" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">rooms/empty.png</t>
+          <t xml:space="preserve">icons/totem.png</t>
         </is>
       </c>
       <c r="E127" t="inlineStr" s="2">
@@ -8143,17 +8143,17 @@
       </c>
       <c r="H127" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">~183x192</t>
+          <t xml:space="preserve">128x128 (shows at 50px)</t>
         </is>
       </c>
       <c r="I127" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">—</t>
+          <t xml:space="preserve">centered, alpha</t>
         </is>
       </c>
       <c r="J127" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">P1</t>
+          <t xml:space="preserve">P2</t>
         </is>
       </c>
       <c r="K127" t="inlineStr" s="6">
@@ -8165,27 +8165,27 @@
     <row r="128">
       <c r="A128" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">Rooms — special</t>
+          <t xml:space="preserve">Card icons</t>
         </is>
       </c>
       <c r="B128" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">Boss cell</t>
+          <t xml:space="preserve">War Camp</t>
         </is>
       </c>
       <c r="C128" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">Throne-room cell dressing</t>
+          <t xml:space="preserve">Hand-card face icon</t>
         </is>
       </c>
       <c r="D128" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">(painted in arena/bg.png)</t>
-        </is>
-      </c>
-      <c r="E128" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">HAVE</t>
+          <t xml:space="preserve">icons/warcamp.png</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr" s="4">
+        <is>
+          <t xml:space="preserve">MISSING</t>
         </is>
       </c>
       <c r="F128" t="inlineStr" s="6">
@@ -8200,12 +8200,12 @@
       </c>
       <c r="H128" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">—</t>
+          <t xml:space="preserve">128x128 (shows at 50px)</t>
         </is>
       </c>
       <c r="I128" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">right edge of scene</t>
+          <t xml:space="preserve">centered, alpha</t>
         </is>
       </c>
       <c r="J128" t="inlineStr" s="6">
@@ -8215,34 +8215,34 @@
       </c>
       <c r="K128" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">Covered by the arena backdrop throne.</t>
+          <t xml:space="preserve">Card shows emoji today — runestone, warcamp, shop &amp; minion are the only gaps.</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">Rooms — special</t>
+          <t xml:space="preserve">Card icons</t>
         </is>
       </c>
       <c r="B129" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">Gate</t>
+          <t xml:space="preserve">Gel Cube</t>
         </is>
       </c>
       <c r="C129" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">Entrance gate / staging area art</t>
+          <t xml:space="preserve">Hand-card face icon</t>
         </is>
       </c>
       <c r="D129" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">rooms/gate.png</t>
-        </is>
-      </c>
-      <c r="E129" t="inlineStr" s="5">
-        <is>
-          <t xml:space="preserve">PROCEDURAL</t>
+          <t xml:space="preserve">icons/slime.png</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">HAVE</t>
         </is>
       </c>
       <c r="F129" t="inlineStr" s="6">
@@ -8257,12 +8257,12 @@
       </c>
       <c r="H129" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">~150x200</t>
+          <t xml:space="preserve">128x128 (shows at 50px)</t>
         </is>
       </c>
       <c r="I129" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">left of room 0</t>
+          <t xml:space="preserve">centered, alpha</t>
         </is>
       </c>
       <c r="J129" t="inlineStr" s="6">
@@ -8272,34 +8272,34 @@
       </c>
       <c r="K129" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">Heroes now march in from outside — a painted gate would sell it.</t>
+          <t xml:space="preserve">Live.</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">Rooms — decals</t>
+          <t xml:space="preserve">Card icons</t>
         </is>
       </c>
       <c r="B130" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">Carnage</t>
+          <t xml:space="preserve">Ogre Lair</t>
         </is>
       </c>
       <c r="C130" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">Blood pools / bones / skulls (kill decals)</t>
+          <t xml:space="preserve">Hand-card face icon</t>
         </is>
       </c>
       <c r="D130" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">rooms/fx/carnage_*.png</t>
-        </is>
-      </c>
-      <c r="E130" t="inlineStr" s="5">
-        <is>
-          <t xml:space="preserve">PROCEDURAL</t>
+          <t xml:space="preserve">icons/ogre.png</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">HAVE</t>
         </is>
       </c>
       <c r="F130" t="inlineStr" s="6">
@@ -8309,27 +8309,27 @@
       </c>
       <c r="G130" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">6-8 variants</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H130" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">24-64 px, alpha</t>
+          <t xml:space="preserve">128x128 (shows at 50px)</t>
         </is>
       </c>
       <c r="I130" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">floor decals</t>
+          <t xml:space="preserve">centered, alpha</t>
         </is>
       </c>
       <c r="J130" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">P3</t>
+          <t xml:space="preserve">P2</t>
         </is>
       </c>
       <c r="K130" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">Procedural deterministic decals today.</t>
+          <t xml:space="preserve">Live.</t>
         </is>
       </c>
     </row>
@@ -8341,7 +8341,7 @@
       </c>
       <c r="B131" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">Spike Pit</t>
+          <t xml:space="preserve">Shop</t>
         </is>
       </c>
       <c r="C131" t="inlineStr" s="6">
@@ -8351,12 +8351,12 @@
       </c>
       <c r="D131" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">icons/spike.png</t>
-        </is>
-      </c>
-      <c r="E131" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">HAVE</t>
+          <t xml:space="preserve">icons/shop.png</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr" s="4">
+        <is>
+          <t xml:space="preserve">MISSING</t>
         </is>
       </c>
       <c r="F131" t="inlineStr" s="6">
@@ -8381,12 +8381,12 @@
       </c>
       <c r="J131" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">P2</t>
+          <t xml:space="preserve">P1</t>
         </is>
       </c>
       <c r="K131" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">Live.</t>
+          <t xml:space="preserve">Card shows emoji today — runestone, warcamp, shop &amp; minion are the only gaps.</t>
         </is>
       </c>
     </row>
@@ -8398,7 +8398,7 @@
       </c>
       <c r="B132" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">Flame Jet</t>
+          <t xml:space="preserve">Corrupted</t>
         </is>
       </c>
       <c r="C132" t="inlineStr" s="6">
@@ -8408,12 +8408,12 @@
       </c>
       <c r="D132" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">icons/flame.png</t>
-        </is>
-      </c>
-      <c r="E132" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">HAVE</t>
+          <t xml:space="preserve">icons/minion.png</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr" s="4">
+        <is>
+          <t xml:space="preserve">MISSING</t>
         </is>
       </c>
       <c r="F132" t="inlineStr" s="6">
@@ -8438,34 +8438,34 @@
       </c>
       <c r="J132" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">P2</t>
+          <t xml:space="preserve">P1</t>
         </is>
       </c>
       <c r="K132" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">Live.</t>
+          <t xml:space="preserve">Card shows emoji today — runestone, warcamp, shop &amp; minion are the only gaps.</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">Card icons</t>
+          <t xml:space="preserve">Town</t>
         </is>
       </c>
       <c r="B133" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">Dart Wall</t>
+          <t xml:space="preserve">Guild House</t>
         </is>
       </c>
       <c r="C133" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">Hand-card face icon</t>
+          <t xml:space="preserve">Building art</t>
         </is>
       </c>
       <c r="D133" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">icons/arrow.png</t>
+          <t xml:space="preserve">town/guild.png</t>
         </is>
       </c>
       <c r="E133" t="inlineStr" s="2">
@@ -8485,44 +8485,44 @@
       </c>
       <c r="H133" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">128x128 (shows at 50px)</t>
+          <t xml:space="preserve">~360 px tall, alpha</t>
         </is>
       </c>
       <c r="I133" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">centered, alpha</t>
+          <t xml:space="preserve">bottom-centred on plot</t>
         </is>
       </c>
       <c r="J133" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">P2</t>
+          <t xml:space="preserve">P1</t>
         </is>
       </c>
       <c r="K133" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">Live.</t>
+          <t xml:space="preserve">Live (cut from your sheets).</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">Card icons</t>
+          <t xml:space="preserve">Town</t>
         </is>
       </c>
       <c r="B134" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">Oil Slick</t>
+          <t xml:space="preserve">Sorcerer</t>
         </is>
       </c>
       <c r="C134" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">Hand-card face icon</t>
+          <t xml:space="preserve">Building art</t>
         </is>
       </c>
       <c r="D134" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">icons/oil.png</t>
+          <t xml:space="preserve">town/sanctum.png</t>
         </is>
       </c>
       <c r="E134" t="inlineStr" s="2">
@@ -8542,44 +8542,44 @@
       </c>
       <c r="H134" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">128x128 (shows at 50px)</t>
+          <t xml:space="preserve">~360 px tall, alpha</t>
         </is>
       </c>
       <c r="I134" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">centered, alpha</t>
+          <t xml:space="preserve">bottom-centred on plot</t>
         </is>
       </c>
       <c r="J134" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">P2</t>
+          <t xml:space="preserve">P1</t>
         </is>
       </c>
       <c r="K134" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">Live.</t>
+          <t xml:space="preserve">Live (cut from your sheets).</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">Card icons</t>
+          <t xml:space="preserve">Town</t>
         </is>
       </c>
       <c r="B135" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">Frost Trap</t>
+          <t xml:space="preserve">The Inn</t>
         </is>
       </c>
       <c r="C135" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">Hand-card face icon</t>
+          <t xml:space="preserve">Building art</t>
         </is>
       </c>
       <c r="D135" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">icons/frost.png</t>
+          <t xml:space="preserve">town/inn.png</t>
         </is>
       </c>
       <c r="E135" t="inlineStr" s="2">
@@ -8599,44 +8599,44 @@
       </c>
       <c r="H135" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">128x128 (shows at 50px)</t>
+          <t xml:space="preserve">~360 px tall, alpha</t>
         </is>
       </c>
       <c r="I135" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">centered, alpha</t>
+          <t xml:space="preserve">bottom-centred on plot</t>
         </is>
       </c>
       <c r="J135" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">P2</t>
+          <t xml:space="preserve">P1</t>
         </is>
       </c>
       <c r="K135" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">Live.</t>
+          <t xml:space="preserve">Live (cut from your sheets).</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">Card icons</t>
+          <t xml:space="preserve">Town</t>
         </is>
       </c>
       <c r="B136" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">Tesla Coil</t>
+          <t xml:space="preserve">Smugglers</t>
         </is>
       </c>
       <c r="C136" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">Hand-card face icon</t>
+          <t xml:space="preserve">Building art</t>
         </is>
       </c>
       <c r="D136" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">icons/tesla.png</t>
+          <t xml:space="preserve">town/den.png</t>
         </is>
       </c>
       <c r="E136" t="inlineStr" s="2">
@@ -8656,44 +8656,44 @@
       </c>
       <c r="H136" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">128x128 (shows at 50px)</t>
+          <t xml:space="preserve">~360 px tall, alpha</t>
         </is>
       </c>
       <c r="I136" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">centered, alpha</t>
+          <t xml:space="preserve">bottom-centred on plot</t>
         </is>
       </c>
       <c r="J136" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">P2</t>
+          <t xml:space="preserve">P1</t>
         </is>
       </c>
       <c r="K136" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">Live.</t>
+          <t xml:space="preserve">Live (cut from your sheets).</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">Card icons</t>
+          <t xml:space="preserve">Town</t>
         </is>
       </c>
       <c r="B137" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">Mage-Bane</t>
+          <t xml:space="preserve">Watchtower</t>
         </is>
       </c>
       <c r="C137" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">Hand-card face icon</t>
+          <t xml:space="preserve">Building art</t>
         </is>
       </c>
       <c r="D137" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">icons/magebane.png</t>
+          <t xml:space="preserve">town/watch.png</t>
         </is>
       </c>
       <c r="E137" t="inlineStr" s="2">
@@ -8713,44 +8713,44 @@
       </c>
       <c r="H137" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">128x128 (shows at 50px)</t>
+          <t xml:space="preserve">~360 px tall, alpha</t>
         </is>
       </c>
       <c r="I137" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">centered, alpha</t>
+          <t xml:space="preserve">bottom-centred on plot</t>
         </is>
       </c>
       <c r="J137" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">P2</t>
+          <t xml:space="preserve">P1</t>
         </is>
       </c>
       <c r="K137" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">Live.</t>
+          <t xml:space="preserve">Live (cut from your sheets).</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">Card icons</t>
+          <t xml:space="preserve">Town</t>
         </is>
       </c>
       <c r="B138" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">Armor Crusher</t>
+          <t xml:space="preserve">Quarry &amp; Mill</t>
         </is>
       </c>
       <c r="C138" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">Hand-card face icon</t>
+          <t xml:space="preserve">Building art</t>
         </is>
       </c>
       <c r="D138" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">icons/maul.png</t>
+          <t xml:space="preserve">town/quarry.png</t>
         </is>
       </c>
       <c r="E138" t="inlineStr" s="2">
@@ -8770,44 +8770,44 @@
       </c>
       <c r="H138" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">128x128 (shows at 50px)</t>
+          <t xml:space="preserve">~360 px tall, alpha</t>
         </is>
       </c>
       <c r="I138" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">centered, alpha</t>
+          <t xml:space="preserve">bottom-centred on plot</t>
         </is>
       </c>
       <c r="J138" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">P2</t>
+          <t xml:space="preserve">P1</t>
         </is>
       </c>
       <c r="K138" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">Live.</t>
+          <t xml:space="preserve">Live (cut from your sheets).</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">Card icons</t>
+          <t xml:space="preserve">Town</t>
         </is>
       </c>
       <c r="B139" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">Gallows</t>
+          <t xml:space="preserve">The Vault</t>
         </is>
       </c>
       <c r="C139" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">Hand-card face icon</t>
+          <t xml:space="preserve">Building art</t>
         </is>
       </c>
       <c r="D139" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">icons/gallows.png</t>
+          <t xml:space="preserve">town/vault.png</t>
         </is>
       </c>
       <c r="E139" t="inlineStr" s="2">
@@ -8827,44 +8827,44 @@
       </c>
       <c r="H139" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">128x128 (shows at 50px)</t>
+          <t xml:space="preserve">~360 px tall, alpha</t>
         </is>
       </c>
       <c r="I139" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">centered, alpha</t>
+          <t xml:space="preserve">bottom-centred on plot</t>
         </is>
       </c>
       <c r="J139" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">P2</t>
+          <t xml:space="preserve">P1</t>
         </is>
       </c>
       <c r="K139" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">Live.</t>
+          <t xml:space="preserve">Live (cut from your sheets).</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">Card icons</t>
+          <t xml:space="preserve">Town</t>
         </is>
       </c>
       <c r="B140" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">Hexward</t>
+          <t xml:space="preserve">Treasury</t>
         </is>
       </c>
       <c r="C140" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">Hand-card face icon</t>
+          <t xml:space="preserve">Building art</t>
         </is>
       </c>
       <c r="D140" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">icons/hexward.png</t>
+          <t xml:space="preserve">town/treasury.png</t>
         </is>
       </c>
       <c r="E140" t="inlineStr" s="2">
@@ -8884,44 +8884,44 @@
       </c>
       <c r="H140" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">128x128 (shows at 50px)</t>
+          <t xml:space="preserve">~360 px tall, alpha</t>
         </is>
       </c>
       <c r="I140" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">centered, alpha</t>
+          <t xml:space="preserve">bottom-centred on plot</t>
         </is>
       </c>
       <c r="J140" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">P2</t>
+          <t xml:space="preserve">P1</t>
         </is>
       </c>
       <c r="K140" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">Live.</t>
+          <t xml:space="preserve">Live (cut from your sheets).</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">Card icons</t>
+          <t xml:space="preserve">Town</t>
         </is>
       </c>
       <c r="B141" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">Bombard</t>
+          <t xml:space="preserve">Dread Obelisk</t>
         </is>
       </c>
       <c r="C141" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">Hand-card face icon</t>
+          <t xml:space="preserve">Building art</t>
         </is>
       </c>
       <c r="D141" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">icons/bombard.png</t>
+          <t xml:space="preserve">town/obelisk.png</t>
         </is>
       </c>
       <c r="E141" t="inlineStr" s="2">
@@ -8941,44 +8941,44 @@
       </c>
       <c r="H141" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">128x128 (shows at 50px)</t>
+          <t xml:space="preserve">~360 px tall, alpha</t>
         </is>
       </c>
       <c r="I141" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">centered, alpha</t>
+          <t xml:space="preserve">bottom-centred on plot</t>
         </is>
       </c>
       <c r="J141" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">P2</t>
+          <t xml:space="preserve">P1</t>
         </is>
       </c>
       <c r="K141" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">Live.</t>
+          <t xml:space="preserve">Live (cut from your sheets).</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">Card icons</t>
+          <t xml:space="preserve">Town</t>
         </is>
       </c>
       <c r="B142" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">Venom Vent</t>
+          <t xml:space="preserve">Dark Library</t>
         </is>
       </c>
       <c r="C142" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">Hand-card face icon</t>
+          <t xml:space="preserve">Building art</t>
         </is>
       </c>
       <c r="D142" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">icons/venom.png</t>
+          <t xml:space="preserve">town/library.png</t>
         </is>
       </c>
       <c r="E142" t="inlineStr" s="2">
@@ -8998,44 +8998,44 @@
       </c>
       <c r="H142" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">128x128 (shows at 50px)</t>
+          <t xml:space="preserve">~360 px tall, alpha</t>
         </is>
       </c>
       <c r="I142" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">centered, alpha</t>
+          <t xml:space="preserve">bottom-centred on plot</t>
         </is>
       </c>
       <c r="J142" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">P2</t>
+          <t xml:space="preserve">P1</t>
         </is>
       </c>
       <c r="K142" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">Live.</t>
+          <t xml:space="preserve">Live (cut from your sheets).</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">Card icons</t>
+          <t xml:space="preserve">Town</t>
         </is>
       </c>
       <c r="B143" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">Acid Sprayer</t>
+          <t xml:space="preserve">Dark Smithy</t>
         </is>
       </c>
       <c r="C143" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">Hand-card face icon</t>
+          <t xml:space="preserve">Building art</t>
         </is>
       </c>
       <c r="D143" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">icons/corrode.png</t>
+          <t xml:space="preserve">town/smithy.png</t>
         </is>
       </c>
       <c r="E143" t="inlineStr" s="2">
@@ -9055,44 +9055,44 @@
       </c>
       <c r="H143" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">128x128 (shows at 50px)</t>
+          <t xml:space="preserve">~360 px tall, alpha</t>
         </is>
       </c>
       <c r="I143" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">centered, alpha</t>
+          <t xml:space="preserve">bottom-centred on plot</t>
         </is>
       </c>
       <c r="J143" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">P2</t>
+          <t xml:space="preserve">P1</t>
         </is>
       </c>
       <c r="K143" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">Live.</t>
+          <t xml:space="preserve">Live (cut from your sheets).</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">Card icons</t>
+          <t xml:space="preserve">Town</t>
         </is>
       </c>
       <c r="B144" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">Hex Brand</t>
+          <t xml:space="preserve">Relic Shrine</t>
         </is>
       </c>
       <c r="C144" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">Hand-card face icon</t>
+          <t xml:space="preserve">Building art</t>
         </is>
       </c>
       <c r="D144" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">icons/hexbrand.png</t>
+          <t xml:space="preserve">town/shrine.png</t>
         </is>
       </c>
       <c r="E144" t="inlineStr" s="2">
@@ -9112,49 +9112,49 @@
       </c>
       <c r="H144" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">128x128 (shows at 50px)</t>
+          <t xml:space="preserve">~360 px tall, alpha</t>
         </is>
       </c>
       <c r="I144" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">centered, alpha</t>
+          <t xml:space="preserve">bottom-centred on plot</t>
         </is>
       </c>
       <c r="J144" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">P2</t>
+          <t xml:space="preserve">P1</t>
         </is>
       </c>
       <c r="K144" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">Live.</t>
+          <t xml:space="preserve">Live (cut from your sheets).</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">Card icons</t>
+          <t xml:space="preserve">Town</t>
         </is>
       </c>
       <c r="B145" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">Runestone</t>
+          <t xml:space="preserve">War Foundry</t>
         </is>
       </c>
       <c r="C145" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">Hand-card face icon</t>
+          <t xml:space="preserve">Building art</t>
         </is>
       </c>
       <c r="D145" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">icons/runestone.png</t>
-        </is>
-      </c>
-      <c r="E145" t="inlineStr" s="4">
-        <is>
-          <t xml:space="preserve">MISSING</t>
+          <t xml:space="preserve">town/foundry.png</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">HAVE</t>
         </is>
       </c>
       <c r="F145" t="inlineStr" s="6">
@@ -9169,12 +9169,12 @@
       </c>
       <c r="H145" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">128x128 (shows at 50px)</t>
+          <t xml:space="preserve">~360 px tall, alpha</t>
         </is>
       </c>
       <c r="I145" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">centered, alpha</t>
+          <t xml:space="preserve">bottom-centred on plot</t>
         </is>
       </c>
       <c r="J145" t="inlineStr" s="6">
@@ -9184,34 +9184,34 @@
       </c>
       <c r="K145" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">Card shows emoji today — runestone, warcamp, shop &amp; minion are the only gaps.</t>
+          <t xml:space="preserve">Live (cut from your sheets).</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">Card icons</t>
+          <t xml:space="preserve">Town</t>
         </is>
       </c>
       <c r="B146" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">Goblin Den</t>
+          <t xml:space="preserve">All buildings</t>
         </is>
       </c>
       <c r="C146" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">Hand-card face icon</t>
+          <t xml:space="preserve">Level-up variants (Lv2/Lv3 dressing)</t>
         </is>
       </c>
       <c r="D146" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">icons/goblin.png</t>
-        </is>
-      </c>
-      <c r="E146" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">HAVE</t>
+          <t xml:space="preserve">town/&lt;id&gt;_lv2.png</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr" s="4">
+        <is>
+          <t xml:space="preserve">MISSING</t>
         </is>
       </c>
       <c r="F146" t="inlineStr" s="6">
@@ -9221,74 +9221,74 @@
       </c>
       <c r="G146" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2 per bld</t>
         </is>
       </c>
       <c r="H146" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">128x128 (shows at 50px)</t>
+          <t xml:space="preserve">~360 px tall</t>
         </is>
       </c>
       <c r="I146" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">centered, alpha</t>
+          <t xml:space="preserve">same footprint</t>
         </is>
       </c>
       <c r="J146" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">P2</t>
+          <t xml:space="preserve">P3</t>
         </is>
       </c>
       <c r="K146" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">Live.</t>
+          <t xml:space="preserve">Buildings only scale 12%/level today.</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">Card icons</t>
+          <t xml:space="preserve">Town</t>
         </is>
       </c>
       <c r="B147" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">Bone Pit</t>
+          <t xml:space="preserve">Villagers</t>
         </is>
       </c>
       <c r="C147" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">Hand-card face icon</t>
+          <t xml:space="preserve">Villager walk sprites (3-4 designs)</t>
         </is>
       </c>
       <c r="D147" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">icons/skeleton.png</t>
-        </is>
-      </c>
-      <c r="E147" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">HAVE</t>
+          <t xml:space="preserve">town/villager_*.png</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr" s="5">
+        <is>
+          <t xml:space="preserve">PROCEDURAL</t>
         </is>
       </c>
       <c r="F147" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">static</t>
+          <t xml:space="preserve">animation</t>
         </is>
       </c>
       <c r="G147" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4 frames each</t>
         </is>
       </c>
       <c r="H147" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">128x128 (shows at 50px)</t>
+          <t xml:space="preserve">~48 px tall</t>
         </is>
       </c>
       <c r="I147" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">centered, alpha</t>
+          <t xml:space="preserve">side view, both dirs</t>
         </is>
       </c>
       <c r="J147" t="inlineStr" s="6">
@@ -9298,34 +9298,34 @@
       </c>
       <c r="K147" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">Live.</t>
+          <t xml:space="preserve">Villagers are procedural dots today; 2 wander per built building.</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">Card icons</t>
+          <t xml:space="preserve">Town</t>
         </is>
       </c>
       <c r="B148" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">Warden</t>
+          <t xml:space="preserve">Plots</t>
         </is>
       </c>
       <c r="C148" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">Hand-card face icon</t>
+          <t xml:space="preserve">Foundation stake marker</t>
         </is>
       </c>
       <c r="D148" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">icons/warden.png</t>
-        </is>
-      </c>
-      <c r="E148" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">HAVE</t>
+          <t xml:space="preserve">town/plot.png</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr" s="5">
+        <is>
+          <t xml:space="preserve">PROCEDURAL</t>
         </is>
       </c>
       <c r="F148" t="inlineStr" s="6">
@@ -9340,49 +9340,49 @@
       </c>
       <c r="H148" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">128x128 (shows at 50px)</t>
+          <t xml:space="preserve">~80x60</t>
         </is>
       </c>
       <c r="I148" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">centered, alpha</t>
+          <t xml:space="preserve">dashed outline today</t>
         </is>
       </c>
       <c r="J148" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">P2</t>
+          <t xml:space="preserve">P3</t>
         </is>
       </c>
       <c r="K148" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">Live.</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">Card icons</t>
+          <t xml:space="preserve">Town</t>
         </is>
       </c>
       <c r="B149" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">War Totem</t>
+          <t xml:space="preserve">UI</t>
         </is>
       </c>
       <c r="C149" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">Hand-card face icon</t>
+          <t xml:space="preserve">Resource icons (wood/stone/shards)</t>
         </is>
       </c>
       <c r="D149" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">icons/totem.png</t>
-        </is>
-      </c>
-      <c r="E149" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">HAVE</t>
+          <t xml:space="preserve">icons/res_*.png</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr" s="5">
+        <is>
+          <t xml:space="preserve">PROCEDURAL</t>
         </is>
       </c>
       <c r="F149" t="inlineStr" s="6">
@@ -9392,17 +9392,17 @@
       </c>
       <c r="G149" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H149" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">128x128 (shows at 50px)</t>
+          <t xml:space="preserve">64x64</t>
         </is>
       </c>
       <c r="I149" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">centered, alpha</t>
+          <t xml:space="preserve">—</t>
         </is>
       </c>
       <c r="J149" t="inlineStr" s="6">
@@ -9412,148 +9412,138 @@
       </c>
       <c r="K149" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">Live.</t>
+          <t xml:space="preserve">Emoji today (🪵🪨🔮).</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">Card icons</t>
+          <t xml:space="preserve">UI chrome</t>
         </is>
       </c>
       <c r="B150" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">War Camp</t>
+          <t xml:space="preserve">Buttons</t>
         </is>
       </c>
       <c r="C150" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">Hand-card face icon</t>
+          <t xml:space="preserve">9-slice pixel button — normal/hover/pressed/disabled</t>
         </is>
       </c>
       <c r="D150" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">icons/warcamp.png</t>
-        </is>
-      </c>
-      <c r="E150" t="inlineStr" s="4">
-        <is>
-          <t xml:space="preserve">MISSING</t>
+          <t xml:space="preserve">ui/btn_purple_9s.png</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr" s="5">
+        <is>
+          <t xml:space="preserve">PROCEDURAL</t>
         </is>
       </c>
       <c r="F150" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">static</t>
+          <t xml:space="preserve">9-slice</t>
         </is>
       </c>
       <c r="G150" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4 states</t>
         </is>
       </c>
       <c r="H150" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">128x128 (shows at 50px)</t>
+          <t xml:space="preserve">48px corners</t>
         </is>
       </c>
       <c r="I150" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">centered, alpha</t>
+          <t xml:space="preserve">P2</t>
         </is>
       </c>
       <c r="J150" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">P1</t>
-        </is>
-      </c>
-      <c r="K150" t="inlineStr" s="6">
-        <is>
-          <t xml:space="preserve">Card shows emoji today — runestone, warcamp, shop &amp; minion are the only gaps.</t>
+          <t xml:space="preserve">CSS pixel-style today (Press Start 2P + hard shadow). Art skin optional.</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">Card icons</t>
+          <t xml:space="preserve">UI chrome</t>
         </is>
       </c>
       <c r="B151" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">Gel Cube</t>
+          <t xml:space="preserve">Buttons</t>
         </is>
       </c>
       <c r="C151" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">Hand-card face icon</t>
+          <t xml:space="preserve">9-slice GO button (green) + BUY (gold) + DANGER (red)</t>
         </is>
       </c>
       <c r="D151" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">icons/slime.png</t>
-        </is>
-      </c>
-      <c r="E151" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">HAVE</t>
+          <t xml:space="preserve">ui/btn_{go,buy,danger}_9s.png</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr" s="5">
+        <is>
+          <t xml:space="preserve">PROCEDURAL</t>
         </is>
       </c>
       <c r="F151" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">static</t>
+          <t xml:space="preserve">9-slice</t>
         </is>
       </c>
       <c r="G151" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3 skins x3 states</t>
         </is>
       </c>
       <c r="H151" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">128x128 (shows at 50px)</t>
+          <t xml:space="preserve">48px corners</t>
         </is>
       </c>
       <c r="I151" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">centered, alpha</t>
+          <t xml:space="preserve">P2</t>
         </is>
       </c>
       <c r="J151" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">P2</t>
-        </is>
-      </c>
-      <c r="K151" t="inlineStr" s="6">
-        <is>
-          <t xml:space="preserve">Live.</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">Card icons</t>
+          <t xml:space="preserve">UI chrome</t>
         </is>
       </c>
       <c r="B152" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">Ogre Lair</t>
+          <t xml:space="preserve">Buttons</t>
         </is>
       </c>
       <c r="C152" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">Hand-card face icon</t>
+          <t xml:space="preserve">Start Game big button (title screen)</t>
         </is>
       </c>
       <c r="D152" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">icons/ogre.png</t>
-        </is>
-      </c>
-      <c r="E152" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">HAVE</t>
+          <t xml:space="preserve">ui/btn_start.png</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr" s="5">
+        <is>
+          <t xml:space="preserve">PROCEDURAL</t>
         </is>
       </c>
       <c r="F152" t="inlineStr" s="6">
@@ -9563,59 +9553,59 @@
       </c>
       <c r="G152" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2 states</t>
         </is>
       </c>
       <c r="H152" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">128x128 (shows at 50px)</t>
+          <t xml:space="preserve">~360x90</t>
         </is>
       </c>
       <c r="I152" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">centered, alpha</t>
+          <t xml:space="preserve">—</t>
         </is>
       </c>
       <c r="J152" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">P2</t>
+          <t xml:space="preserve">P3</t>
         </is>
       </c>
       <c r="K152" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">Live.</t>
+          <t xml:space="preserve">Red CSS button today.</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">Card icons</t>
+          <t xml:space="preserve">UI chrome</t>
         </is>
       </c>
       <c r="B153" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">Shop</t>
+          <t xml:space="preserve">Panels</t>
         </is>
       </c>
       <c r="C153" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">Hand-card face icon</t>
+          <t xml:space="preserve">Overlay panel frame (menus) 9-slice</t>
         </is>
       </c>
       <c r="D153" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">icons/shop.png</t>
-        </is>
-      </c>
-      <c r="E153" t="inlineStr" s="4">
-        <is>
-          <t xml:space="preserve">MISSING</t>
+          <t xml:space="preserve">ui/panel_9s.png</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr" s="5">
+        <is>
+          <t xml:space="preserve">PROCEDURAL</t>
         </is>
       </c>
       <c r="F153" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">static</t>
+          <t xml:space="preserve">9-slice</t>
         </is>
       </c>
       <c r="G153" t="inlineStr" s="6">
@@ -9625,54 +9615,54 @@
       </c>
       <c r="H153" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">128x128 (shows at 50px)</t>
+          <t xml:space="preserve">64px corners</t>
         </is>
       </c>
       <c r="I153" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">centered, alpha</t>
+          <t xml:space="preserve">—</t>
         </is>
       </c>
       <c r="J153" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">P1</t>
+          <t xml:space="preserve">P2</t>
         </is>
       </c>
       <c r="K153" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">Card shows emoji today — runestone, warcamp, shop &amp; minion are the only gaps.</t>
+          <t xml:space="preserve">Flat dark CSS today.</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">Card icons</t>
+          <t xml:space="preserve">UI chrome</t>
         </is>
       </c>
       <c r="B154" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">Corrupted</t>
+          <t xml:space="preserve">Panels</t>
         </is>
       </c>
       <c r="C154" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">Hand-card face icon</t>
+          <t xml:space="preserve">Inspect bubble frame</t>
         </is>
       </c>
       <c r="D154" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">icons/minion.png</t>
-        </is>
-      </c>
-      <c r="E154" t="inlineStr" s="4">
-        <is>
-          <t xml:space="preserve">MISSING</t>
+          <t xml:space="preserve">ui/bubble_9s.png</t>
+        </is>
+      </c>
+      <c r="E154" t="inlineStr" s="5">
+        <is>
+          <t xml:space="preserve">PROCEDURAL</t>
         </is>
       </c>
       <c r="F154" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">static</t>
+          <t xml:space="preserve">9-slice</t>
         </is>
       </c>
       <c r="G154" t="inlineStr" s="6">
@@ -9682,54 +9672,54 @@
       </c>
       <c r="H154" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">128x128 (shows at 50px)</t>
+          <t xml:space="preserve">32px corners</t>
         </is>
       </c>
       <c r="I154" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">centered, alpha</t>
+          <t xml:space="preserve">arrow optional</t>
         </is>
       </c>
       <c r="J154" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">P1</t>
+          <t xml:space="preserve">P3</t>
         </is>
       </c>
       <c r="K154" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">Card shows emoji today — runestone, warcamp, shop &amp; minion are the only gaps.</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">Town</t>
+          <t xml:space="preserve">UI chrome</t>
         </is>
       </c>
       <c r="B155" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">Guild House</t>
+          <t xml:space="preserve">Panels</t>
         </is>
       </c>
       <c r="C155" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">Building art</t>
+          <t xml:space="preserve">Choice/slot card frame</t>
         </is>
       </c>
       <c r="D155" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">town/guild.png</t>
-        </is>
-      </c>
-      <c r="E155" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">HAVE</t>
+          <t xml:space="preserve">ui/choice_9s.png</t>
+        </is>
+      </c>
+      <c r="E155" t="inlineStr" s="5">
+        <is>
+          <t xml:space="preserve">PROCEDURAL</t>
         </is>
       </c>
       <c r="F155" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">static</t>
+          <t xml:space="preserve">9-slice</t>
         </is>
       </c>
       <c r="G155" t="inlineStr" s="6">
@@ -9739,49 +9729,49 @@
       </c>
       <c r="H155" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">~360 px tall, alpha</t>
+          <t xml:space="preserve">—</t>
         </is>
       </c>
       <c r="I155" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">bottom-centred on plot</t>
+          <t xml:space="preserve">—</t>
         </is>
       </c>
       <c r="J155" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">P1</t>
+          <t xml:space="preserve">P3</t>
         </is>
       </c>
       <c r="K155" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">Live (cut from your sheets).</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">Town</t>
+          <t xml:space="preserve">UI chrome</t>
         </is>
       </c>
       <c r="B156" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">Sorcerer</t>
+          <t xml:space="preserve">Cards</t>
         </is>
       </c>
       <c r="C156" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">Building art</t>
+          <t xml:space="preserve">Hand-card frame + 5 rarity borders</t>
         </is>
       </c>
       <c r="D156" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">town/sanctum.png</t>
-        </is>
-      </c>
-      <c r="E156" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">HAVE</t>
+          <t xml:space="preserve">ui/card_{tier}.png</t>
+        </is>
+      </c>
+      <c r="E156" t="inlineStr" s="5">
+        <is>
+          <t xml:space="preserve">PROCEDURAL</t>
         </is>
       </c>
       <c r="F156" t="inlineStr" s="6">
@@ -9791,54 +9781,54 @@
       </c>
       <c r="G156" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="H156" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">~360 px tall, alpha</t>
+          <t xml:space="preserve">~140x180</t>
         </is>
       </c>
       <c r="I156" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">bottom-centred on plot</t>
+          <t xml:space="preserve">common/special/rare/epic/legendary</t>
         </is>
       </c>
       <c r="J156" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">P1</t>
+          <t xml:space="preserve">P2</t>
         </is>
       </c>
       <c r="K156" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">Live (cut from your sheets).</t>
+          <t xml:space="preserve">Rarity is a colored CSS border today.</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">Town</t>
+          <t xml:space="preserve">UI chrome</t>
         </is>
       </c>
       <c r="B157" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">The Inn</t>
+          <t xml:space="preserve">Bars</t>
         </is>
       </c>
       <c r="C157" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">Building art</t>
+          <t xml:space="preserve">Boss HP + mana bar frame &amp; fills</t>
         </is>
       </c>
       <c r="D157" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">town/inn.png</t>
-        </is>
-      </c>
-      <c r="E157" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">HAVE</t>
+          <t xml:space="preserve">ui/bar_*.png</t>
+        </is>
+      </c>
+      <c r="E157" t="inlineStr" s="5">
+        <is>
+          <t xml:space="preserve">PROCEDURAL</t>
         </is>
       </c>
       <c r="F157" t="inlineStr" s="6">
@@ -9848,54 +9838,54 @@
       </c>
       <c r="G157" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="H157" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">~360 px tall, alpha</t>
+          <t xml:space="preserve">~280x28</t>
         </is>
       </c>
       <c r="I157" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">bottom-centred on plot</t>
+          <t xml:space="preserve">—</t>
         </is>
       </c>
       <c r="J157" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">P1</t>
+          <t xml:space="preserve">P2</t>
         </is>
       </c>
       <c r="K157" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">Live (cut from your sheets).</t>
+          <t xml:space="preserve">Canvas-drawn.</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">Town</t>
+          <t xml:space="preserve">UI chrome</t>
         </is>
       </c>
       <c r="B158" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">Smugglers</t>
+          <t xml:space="preserve">Bars</t>
         </is>
       </c>
       <c r="C158" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">Building art</t>
+          <t xml:space="preserve">Hero mini HP bar</t>
         </is>
       </c>
       <c r="D158" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">town/den.png</t>
-        </is>
-      </c>
-      <c r="E158" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">HAVE</t>
+          <t xml:space="preserve">ui/minibar.png</t>
+        </is>
+      </c>
+      <c r="E158" t="inlineStr" s="5">
+        <is>
+          <t xml:space="preserve">PROCEDURAL</t>
         </is>
       </c>
       <c r="F158" t="inlineStr" s="6">
@@ -9910,49 +9900,49 @@
       </c>
       <c r="H158" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">~360 px tall, alpha</t>
+          <t xml:space="preserve">~60x8</t>
         </is>
       </c>
       <c r="I158" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">bottom-centred on plot</t>
+          <t xml:space="preserve">—</t>
         </is>
       </c>
       <c r="J158" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">P1</t>
+          <t xml:space="preserve">P3</t>
         </is>
       </c>
       <c r="K158" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">Live (cut from your sheets).</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">Town</t>
+          <t xml:space="preserve">UI chrome</t>
         </is>
       </c>
       <c r="B159" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">Watchtower</t>
+          <t xml:space="preserve">HUD</t>
         </is>
       </c>
       <c r="C159" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">Building art</t>
+          <t xml:space="preserve">Ability button frame + cooldown sweep</t>
         </is>
       </c>
       <c r="D159" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">town/watch.png</t>
-        </is>
-      </c>
-      <c r="E159" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">HAVE</t>
+          <t xml:space="preserve">ui/abil_frame.png</t>
+        </is>
+      </c>
+      <c r="E159" t="inlineStr" s="5">
+        <is>
+          <t xml:space="preserve">PROCEDURAL</t>
         </is>
       </c>
       <c r="F159" t="inlineStr" s="6">
@@ -9962,54 +9952,54 @@
       </c>
       <c r="G159" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H159" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">~360 px tall, alpha</t>
+          <t xml:space="preserve">96x96</t>
         </is>
       </c>
       <c r="I159" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">bottom-centred on plot</t>
+          <t xml:space="preserve">radial sweep overlay</t>
         </is>
       </c>
       <c r="J159" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">P1</t>
+          <t xml:space="preserve">P2</t>
         </is>
       </c>
       <c r="K159" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">Live (cut from your sheets).</t>
+          <t xml:space="preserve">Emoji icon inside.</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">Town</t>
+          <t xml:space="preserve">UI chrome</t>
         </is>
       </c>
       <c r="B160" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">Quarry &amp; Mill</t>
+          <t xml:space="preserve">HUD</t>
         </is>
       </c>
       <c r="C160" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">Building art</t>
+          <t xml:space="preserve">Relic-bar slot frame</t>
         </is>
       </c>
       <c r="D160" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">town/quarry.png</t>
-        </is>
-      </c>
-      <c r="E160" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">HAVE</t>
+          <t xml:space="preserve">ui/relic_slot.png</t>
+        </is>
+      </c>
+      <c r="E160" t="inlineStr" s="5">
+        <is>
+          <t xml:space="preserve">PROCEDURAL</t>
         </is>
       </c>
       <c r="F160" t="inlineStr" s="6">
@@ -10024,54 +10014,54 @@
       </c>
       <c r="H160" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">~360 px tall, alpha</t>
+          <t xml:space="preserve">56x56</t>
         </is>
       </c>
       <c r="I160" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">bottom-centred on plot</t>
+          <t xml:space="preserve">—</t>
         </is>
       </c>
       <c r="J160" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">P1</t>
+          <t xml:space="preserve">P3</t>
         </is>
       </c>
       <c r="K160" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">Live (cut from your sheets).</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">Town</t>
+          <t xml:space="preserve">UI chrome</t>
         </is>
       </c>
       <c r="B161" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">The Vault</t>
+          <t xml:space="preserve">HUD</t>
         </is>
       </c>
       <c r="C161" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">Building art</t>
+          <t xml:space="preserve">Top bar backplate</t>
         </is>
       </c>
       <c r="D161" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">town/vault.png</t>
-        </is>
-      </c>
-      <c r="E161" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">HAVE</t>
+          <t xml:space="preserve">ui/topbar_9s.png</t>
+        </is>
+      </c>
+      <c r="E161" t="inlineStr" s="5">
+        <is>
+          <t xml:space="preserve">PROCEDURAL</t>
         </is>
       </c>
       <c r="F161" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">static</t>
+          <t xml:space="preserve">9-slice</t>
         </is>
       </c>
       <c r="G161" t="inlineStr" s="6">
@@ -10081,49 +10071,49 @@
       </c>
       <c r="H161" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">~360 px tall, alpha</t>
+          <t xml:space="preserve">—</t>
         </is>
       </c>
       <c r="I161" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">bottom-centred on plot</t>
+          <t xml:space="preserve">—</t>
         </is>
       </c>
       <c r="J161" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">P1</t>
+          <t xml:space="preserve">P3</t>
         </is>
       </c>
       <c r="K161" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">Live (cut from your sheets).</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">Town</t>
+          <t xml:space="preserve">UI chrome</t>
         </is>
       </c>
       <c r="B162" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">Treasury</t>
+          <t xml:space="preserve">HUD</t>
         </is>
       </c>
       <c r="C162" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">Building art</t>
+          <t xml:space="preserve">Zoom +/- , pause ☰, audio 🔊 button icons</t>
         </is>
       </c>
       <c r="D162" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">town/treasury.png</t>
-        </is>
-      </c>
-      <c r="E162" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">HAVE</t>
+          <t xml:space="preserve">ui/ico_{zoom,pause,audio}.png</t>
+        </is>
+      </c>
+      <c r="E162" t="inlineStr" s="5">
+        <is>
+          <t xml:space="preserve">PROCEDURAL</t>
         </is>
       </c>
       <c r="F162" t="inlineStr" s="6">
@@ -10133,54 +10123,54 @@
       </c>
       <c r="G162" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="H162" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">~360 px tall, alpha</t>
+          <t xml:space="preserve">64x64</t>
         </is>
       </c>
       <c r="I162" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">bottom-centred on plot</t>
+          <t xml:space="preserve">—</t>
         </is>
       </c>
       <c r="J162" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">P1</t>
+          <t xml:space="preserve">P3</t>
         </is>
       </c>
       <c r="K162" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">Live (cut from your sheets).</t>
+          <t xml:space="preserve">Emoji/CSS today.</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">Town</t>
+          <t xml:space="preserve">UI chrome</t>
         </is>
       </c>
       <c r="B163" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">Dread Obelisk</t>
+          <t xml:space="preserve">Banners</t>
         </is>
       </c>
       <c r="C163" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">Building art</t>
+          <t xml:space="preserve">Arrival banner ribbon (champion/rival/king)</t>
         </is>
       </c>
       <c r="D163" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">town/obelisk.png</t>
-        </is>
-      </c>
-      <c r="E163" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">HAVE</t>
+          <t xml:space="preserve">ui/banner_ribbon.png</t>
+        </is>
+      </c>
+      <c r="E163" t="inlineStr" s="5">
+        <is>
+          <t xml:space="preserve">PROCEDURAL</t>
         </is>
       </c>
       <c r="F163" t="inlineStr" s="6">
@@ -10190,111 +10180,111 @@
       </c>
       <c r="G163" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H163" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">~360 px tall, alpha</t>
+          <t xml:space="preserve">~900x160</t>
         </is>
       </c>
       <c r="I163" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">bottom-centred on plot</t>
+          <t xml:space="preserve">center sweep</t>
         </is>
       </c>
       <c r="J163" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">P1</t>
+          <t xml:space="preserve">P2</t>
         </is>
       </c>
       <c r="K163" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">Live (cut from your sheets).</t>
+          <t xml:space="preserve">Canvas gradient banner today.</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">Town</t>
+          <t xml:space="preserve">UI chrome</t>
         </is>
       </c>
       <c r="B164" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">Dark Library</t>
+          <t xml:space="preserve">Feedback</t>
         </is>
       </c>
       <c r="C164" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">Building art</t>
+          <t xml:space="preserve">Tutorial pulse / pointer hand</t>
         </is>
       </c>
       <c r="D164" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">town/library.png</t>
-        </is>
-      </c>
-      <c r="E164" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">HAVE</t>
+          <t xml:space="preserve">ui/pointer.png</t>
+        </is>
+      </c>
+      <c r="E164" t="inlineStr" s="5">
+        <is>
+          <t xml:space="preserve">PROCEDURAL</t>
         </is>
       </c>
       <c r="F164" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">static</t>
+          <t xml:space="preserve">animation</t>
         </is>
       </c>
       <c r="G164" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H164" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">~360 px tall, alpha</t>
+          <t xml:space="preserve">64x64</t>
         </is>
       </c>
       <c r="I164" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">bottom-centred on plot</t>
+          <t xml:space="preserve">—</t>
         </is>
       </c>
       <c r="J164" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">P1</t>
+          <t xml:space="preserve">P3</t>
         </is>
       </c>
       <c r="K164" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">Live (cut from your sheets).</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">Town</t>
+          <t xml:space="preserve">UI chrome</t>
         </is>
       </c>
       <c r="B165" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">Dark Smithy</t>
+          <t xml:space="preserve">Cursor</t>
         </is>
       </c>
       <c r="C165" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">Building art</t>
+          <t xml:space="preserve">Custom cursor + grab cursor</t>
         </is>
       </c>
       <c r="D165" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">town/smithy.png</t>
-        </is>
-      </c>
-      <c r="E165" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">HAVE</t>
+          <t xml:space="preserve">ui/cursor_*.png</t>
+        </is>
+      </c>
+      <c r="E165" t="inlineStr" s="4">
+        <is>
+          <t xml:space="preserve">MISSING</t>
         </is>
       </c>
       <c r="F165" t="inlineStr" s="6">
@@ -10304,54 +10294,54 @@
       </c>
       <c r="G165" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H165" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">~360 px tall, alpha</t>
+          <t xml:space="preserve">32x32</t>
         </is>
       </c>
       <c r="I165" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">bottom-centred on plot</t>
+          <t xml:space="preserve">hotspot top-left</t>
         </is>
       </c>
       <c r="J165" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">P1</t>
+          <t xml:space="preserve">P3</t>
         </is>
       </c>
       <c r="K165" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">Live (cut from your sheets).</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">Town</t>
+          <t xml:space="preserve">Icon sets</t>
         </is>
       </c>
       <c r="B166" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">Relic Shrine</t>
+          <t xml:space="preserve">Currencies</t>
         </is>
       </c>
       <c r="C166" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">Building art</t>
+          <t xml:space="preserve">Gold / Dread / Mana / HP icons</t>
         </is>
       </c>
       <c r="D166" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">town/shrine.png</t>
-        </is>
-      </c>
-      <c r="E166" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">HAVE</t>
+          <t xml:space="preserve">icons/cur_*.png</t>
+        </is>
+      </c>
+      <c r="E166" t="inlineStr" s="5">
+        <is>
+          <t xml:space="preserve">PROCEDURAL</t>
         </is>
       </c>
       <c r="F166" t="inlineStr" s="6">
@@ -10361,54 +10351,54 @@
       </c>
       <c r="G166" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="H166" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">~360 px tall, alpha</t>
+          <t xml:space="preserve">64x64</t>
         </is>
       </c>
       <c r="I166" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">bottom-centred on plot</t>
+          <t xml:space="preserve">—</t>
         </is>
       </c>
       <c r="J166" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">P1</t>
+          <t xml:space="preserve">P2</t>
         </is>
       </c>
       <c r="K166" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">Live (cut from your sheets).</t>
+          <t xml:space="preserve">Emoji today (💰😈🔮❤️).</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">Town</t>
+          <t xml:space="preserve">Icon sets</t>
         </is>
       </c>
       <c r="B167" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">War Foundry</t>
+          <t xml:space="preserve">Currencies</t>
         </is>
       </c>
       <c r="C167" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">Building art</t>
+          <t xml:space="preserve">Rune points ◆ / lifetime kills ☠ / ascension crown</t>
         </is>
       </c>
       <c r="D167" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">town/foundry.png</t>
-        </is>
-      </c>
-      <c r="E167" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">HAVE</t>
+          <t xml:space="preserve">icons/meta_*.png</t>
+        </is>
+      </c>
+      <c r="E167" t="inlineStr" s="5">
+        <is>
+          <t xml:space="preserve">PROCEDURAL</t>
         </is>
       </c>
       <c r="F167" t="inlineStr" s="6">
@@ -10418,54 +10408,54 @@
       </c>
       <c r="G167" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H167" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">~360 px tall, alpha</t>
+          <t xml:space="preserve">64x64</t>
         </is>
       </c>
       <c r="I167" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">bottom-centred on plot</t>
+          <t xml:space="preserve">—</t>
         </is>
       </c>
       <c r="J167" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">P1</t>
+          <t xml:space="preserve">P3</t>
         </is>
       </c>
       <c r="K167" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">Live (cut from your sheets).</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">Town</t>
+          <t xml:space="preserve">Icon sets</t>
         </is>
       </c>
       <c r="B168" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">All buildings</t>
+          <t xml:space="preserve">Abilities</t>
         </is>
       </c>
       <c r="C168" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">Level-up variants (Lv2/Lv3 dressing)</t>
+          <t xml:space="preserve">14 boss-ability icons (slam, fire breath, bone bolt, curse, freeze, drain, dread, mend, quake, hellfire, mana siphon, devour, raise dead, entangle)</t>
         </is>
       </c>
       <c r="D168" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">town/&lt;id&gt;_lv2.png</t>
-        </is>
-      </c>
-      <c r="E168" t="inlineStr" s="4">
-        <is>
-          <t xml:space="preserve">MISSING</t>
+          <t xml:space="preserve">icons/abil_*.png</t>
+        </is>
+      </c>
+      <c r="E168" t="inlineStr" s="5">
+        <is>
+          <t xml:space="preserve">PROCEDURAL</t>
         </is>
       </c>
       <c r="F168" t="inlineStr" s="6">
@@ -10475,49 +10465,49 @@
       </c>
       <c r="G168" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">2 per bld</t>
+          <t xml:space="preserve">14</t>
         </is>
       </c>
       <c r="H168" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">~360 px tall</t>
+          <t xml:space="preserve">96x96</t>
         </is>
       </c>
       <c r="I168" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">same footprint</t>
+          <t xml:space="preserve">—</t>
         </is>
       </c>
       <c r="J168" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">P3</t>
+          <t xml:space="preserve">P2</t>
         </is>
       </c>
       <c r="K168" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">Buildings only scale 12%/level today.</t>
+          <t xml:space="preserve">Emoji today; painted set = big HUD upgrade.</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">Town</t>
+          <t xml:space="preserve">Icon sets</t>
         </is>
       </c>
       <c r="B169" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">Villagers</t>
+          <t xml:space="preserve">Relics</t>
         </is>
       </c>
       <c r="C169" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">Villager walk sprites (3-4 designs)</t>
+          <t xml:space="preserve">33 relic icons across 5 tiers (common/special/rare/epic/legendary)</t>
         </is>
       </c>
       <c r="D169" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">town/villager_*.png</t>
+          <t xml:space="preserve">icons/relic_*.png</t>
         </is>
       </c>
       <c r="E169" t="inlineStr" s="5">
@@ -10527,54 +10517,54 @@
       </c>
       <c r="F169" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">animation</t>
+          <t xml:space="preserve">static</t>
         </is>
       </c>
       <c r="G169" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">4 frames each</t>
+          <t xml:space="preserve">33</t>
         </is>
       </c>
       <c r="H169" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">~48 px tall</t>
+          <t xml:space="preserve">96x96</t>
         </is>
       </c>
       <c r="I169" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">side view, both dirs</t>
+          <t xml:space="preserve">tier border separate</t>
         </is>
       </c>
       <c r="J169" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">P2</t>
+          <t xml:space="preserve">P3</t>
         </is>
       </c>
       <c r="K169" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">Villagers are procedural dots today; 2 wander per built building.</t>
+          <t xml:space="preserve">Emoji today.</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">Town</t>
+          <t xml:space="preserve">Icon sets</t>
         </is>
       </c>
       <c r="B170" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">Plots</t>
+          <t xml:space="preserve">Traits</t>
         </is>
       </c>
       <c r="C170" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">Foundation stake marker</t>
+          <t xml:space="preserve">6 elite-trait icons (hardy/berserker/armored/swift/vampiric/zealot)</t>
         </is>
       </c>
       <c r="D170" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">town/plot.png</t>
+          <t xml:space="preserve">icons/trait_*.png</t>
         </is>
       </c>
       <c r="E170" t="inlineStr" s="5">
@@ -10589,17 +10579,17 @@
       </c>
       <c r="G170" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="H170" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">~80x60</t>
+          <t xml:space="preserve">48x48</t>
         </is>
       </c>
       <c r="I170" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">dashed outline today</t>
+          <t xml:space="preserve">—</t>
         </is>
       </c>
       <c r="J170" t="inlineStr" s="6">
@@ -10616,22 +10606,22 @@
     <row r="171">
       <c r="A171" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">Town</t>
+          <t xml:space="preserve">Icon sets</t>
         </is>
       </c>
       <c r="B171" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">UI</t>
+          <t xml:space="preserve">Edicts</t>
         </is>
       </c>
       <c r="C171" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">Resource icons (wood/stone/shards)</t>
+          <t xml:space="preserve">7 edict icons</t>
         </is>
       </c>
       <c r="D171" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">icons/res_*.png</t>
+          <t xml:space="preserve">icons/edict_*.png</t>
         </is>
       </c>
       <c r="E171" t="inlineStr" s="5">
@@ -10646,12 +10636,12 @@
       </c>
       <c r="G171" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="H171" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">64x64</t>
+          <t xml:space="preserve">96x96</t>
         </is>
       </c>
       <c r="I171" t="inlineStr" s="6">
@@ -10661,34 +10651,34 @@
       </c>
       <c r="J171" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">P2</t>
+          <t xml:space="preserve">P3</t>
         </is>
       </c>
       <c r="K171" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">Emoji today (🪵🪨🔮).</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">UI chrome</t>
+          <t xml:space="preserve">Icon sets</t>
         </is>
       </c>
       <c r="B172" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">Buttons</t>
+          <t xml:space="preserve">Mandates</t>
         </is>
       </c>
       <c r="C172" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">9-slice pixel button — normal/hover/pressed/disabled</t>
+          <t xml:space="preserve">10 mandate icons</t>
         </is>
       </c>
       <c r="D172" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">ui/btn_purple_9s.png</t>
+          <t xml:space="preserve">icons/mandate_*.png</t>
         </is>
       </c>
       <c r="E172" t="inlineStr" s="5">
@@ -10698,49 +10688,54 @@
       </c>
       <c r="F172" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">9-slice</t>
+          <t xml:space="preserve">static</t>
         </is>
       </c>
       <c r="G172" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">4 states</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="H172" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">48px corners</t>
+          <t xml:space="preserve">96x96</t>
         </is>
       </c>
       <c r="I172" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">P2</t>
+          <t xml:space="preserve">—</t>
         </is>
       </c>
       <c r="J172" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">CSS pixel-style today (Press Start 2P + hard shadow). Art skin optional.</t>
+          <t xml:space="preserve">P3</t>
+        </is>
+      </c>
+      <c r="K172" t="inlineStr" s="6">
+        <is>
+          <t xml:space="preserve"/>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">UI chrome</t>
+          <t xml:space="preserve">Icon sets</t>
         </is>
       </c>
       <c r="B173" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">Buttons</t>
+          <t xml:space="preserve">Doctrines</t>
         </is>
       </c>
       <c r="C173" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">9-slice GO button (green) + BUY (gold) + DANGER (red)</t>
+          <t xml:space="preserve">6 boss-doctrine icons</t>
         </is>
       </c>
       <c r="D173" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">ui/btn_{go,buy,danger}_9s.png</t>
+          <t xml:space="preserve">icons/doc_*.png</t>
         </is>
       </c>
       <c r="E173" t="inlineStr" s="5">
@@ -10750,25 +10745,30 @@
       </c>
       <c r="F173" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">9-slice</t>
+          <t xml:space="preserve">static</t>
         </is>
       </c>
       <c r="G173" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">3 skins x3 states</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="H173" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">48px corners</t>
+          <t xml:space="preserve">96x96</t>
         </is>
       </c>
       <c r="I173" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">P2</t>
+          <t xml:space="preserve">—</t>
         </is>
       </c>
       <c r="J173" t="inlineStr" s="6">
+        <is>
+          <t xml:space="preserve">P3</t>
+        </is>
+      </c>
+      <c r="K173" t="inlineStr" s="6">
         <is>
           <t xml:space="preserve"/>
         </is>
@@ -10777,22 +10777,22 @@
     <row r="174">
       <c r="A174" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">UI chrome</t>
+          <t xml:space="preserve">Icon sets</t>
         </is>
       </c>
       <c r="B174" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">Buttons</t>
+          <t xml:space="preserve">Runes</t>
         </is>
       </c>
       <c r="C174" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">Start Game big button (title screen)</t>
+          <t xml:space="preserve">19 rune-tree node icons</t>
         </is>
       </c>
       <c r="D174" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">ui/btn_start.png</t>
+          <t xml:space="preserve">icons/rune_*.png</t>
         </is>
       </c>
       <c r="E174" t="inlineStr" s="5">
@@ -10807,12 +10807,12 @@
       </c>
       <c r="G174" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">2 states</t>
+          <t xml:space="preserve">19</t>
         </is>
       </c>
       <c r="H174" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">~360x90</t>
+          <t xml:space="preserve">96x96</t>
         </is>
       </c>
       <c r="I174" t="inlineStr" s="6">
@@ -10827,29 +10827,29 @@
       </c>
       <c r="K174" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">Red CSS button today.</t>
+          <t xml:space="preserve">Rune page uses emoji nodes.</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">UI chrome</t>
+          <t xml:space="preserve">Icon sets</t>
         </is>
       </c>
       <c r="B175" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">Panels</t>
+          <t xml:space="preserve">Classes</t>
         </is>
       </c>
       <c r="C175" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">Overlay panel frame (menus) 9-slice</t>
+          <t xml:space="preserve">4 hero-class icons (warrior/rogue/mage/cleric)</t>
         </is>
       </c>
       <c r="D175" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">ui/panel_9s.png</t>
+          <t xml:space="preserve">icons/cls_*.png</t>
         </is>
       </c>
       <c r="E175" t="inlineStr" s="5">
@@ -10859,17 +10859,17 @@
       </c>
       <c r="F175" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">9-slice</t>
+          <t xml:space="preserve">static</t>
         </is>
       </c>
       <c r="G175" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="H175" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">64px corners</t>
+          <t xml:space="preserve">64x64</t>
         </is>
       </c>
       <c r="I175" t="inlineStr" s="6">
@@ -10879,34 +10879,34 @@
       </c>
       <c r="J175" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">P2</t>
+          <t xml:space="preserve">P3</t>
         </is>
       </c>
       <c r="K175" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">Flat dark CSS today.</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">UI chrome</t>
+          <t xml:space="preserve">Icon sets</t>
         </is>
       </c>
       <c r="B176" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">Panels</t>
+          <t xml:space="preserve">Elements</t>
         </is>
       </c>
       <c r="C176" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">Inspect bubble frame</t>
+          <t xml:space="preserve">7 element icons (phys/fire/ice/oil/shock/poison/acid)</t>
         </is>
       </c>
       <c r="D176" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">ui/bubble_9s.png</t>
+          <t xml:space="preserve">icons/elem_*.png</t>
         </is>
       </c>
       <c r="E176" t="inlineStr" s="5">
@@ -10916,54 +10916,54 @@
       </c>
       <c r="F176" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">9-slice</t>
+          <t xml:space="preserve">static</t>
         </is>
       </c>
       <c r="G176" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="H176" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">32px corners</t>
+          <t xml:space="preserve">48x48</t>
         </is>
       </c>
       <c r="I176" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">arrow optional</t>
+          <t xml:space="preserve">—</t>
         </is>
       </c>
       <c r="J176" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">P3</t>
+          <t xml:space="preserve">P2</t>
         </is>
       </c>
       <c r="K176" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Used in tooltips &amp; codex.</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">UI chrome</t>
+          <t xml:space="preserve">Icon sets</t>
         </is>
       </c>
       <c r="B177" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">Panels</t>
+          <t xml:space="preserve">Reactions</t>
         </is>
       </c>
       <c r="C177" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">Choice/slot card frame</t>
+          <t xml:space="preserve">Reaction icons (shatter/ignite/detonate/conduct/melt)</t>
         </is>
       </c>
       <c r="D177" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">ui/choice_9s.png</t>
+          <t xml:space="preserve">icons/react_*.png</t>
         </is>
       </c>
       <c r="E177" t="inlineStr" s="5">
@@ -10973,17 +10973,17 @@
       </c>
       <c r="F177" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">9-slice</t>
+          <t xml:space="preserve">static</t>
         </is>
       </c>
       <c r="G177" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="H177" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">—</t>
+          <t xml:space="preserve">48x48</t>
         </is>
       </c>
       <c r="I177" t="inlineStr" s="6">
@@ -11005,22 +11005,22 @@
     <row r="178">
       <c r="A178" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">UI chrome</t>
+          <t xml:space="preserve">VFX &amp; animations</t>
         </is>
       </c>
       <c r="B178" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">Cards</t>
+          <t xml:space="preserve">Elemental</t>
         </is>
       </c>
       <c r="C178" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">Hand-card frame + 5 rarity borders</t>
+          <t xml:space="preserve">Burn flame loop (on hero)</t>
         </is>
       </c>
       <c r="D178" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">ui/card_{tier}.png</t>
+          <t xml:space="preserve">fx/burn_0..3.png</t>
         </is>
       </c>
       <c r="E178" t="inlineStr" s="5">
@@ -11030,54 +11030,49 @@
       </c>
       <c r="F178" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">static</t>
+          <t xml:space="preserve">animation</t>
         </is>
       </c>
       <c r="G178" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="H178" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">~140x180</t>
+          <t xml:space="preserve">48px</t>
         </is>
       </c>
       <c r="I178" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">common/special/rare/epic/legendary</t>
+          <t xml:space="preserve">overlay</t>
         </is>
       </c>
       <c r="J178" t="inlineStr" s="6">
         <is>
           <t xml:space="preserve">P2</t>
-        </is>
-      </c>
-      <c r="K178" t="inlineStr" s="6">
-        <is>
-          <t xml:space="preserve">Rarity is a colored CSS border today.</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">UI chrome</t>
+          <t xml:space="preserve">VFX &amp; animations</t>
         </is>
       </c>
       <c r="B179" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">Bars</t>
+          <t xml:space="preserve">Elemental</t>
         </is>
       </c>
       <c r="C179" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">Boss HP + mana bar frame &amp; fills</t>
+          <t xml:space="preserve">Freeze block + shatter burst</t>
         </is>
       </c>
       <c r="D179" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">ui/bar_*.png</t>
+          <t xml:space="preserve">fx/freeze.png + shatter_0..4.png</t>
         </is>
       </c>
       <c r="E179" t="inlineStr" s="5">
@@ -11087,54 +11082,49 @@
       </c>
       <c r="F179" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">static</t>
+          <t xml:space="preserve">animation</t>
         </is>
       </c>
       <c r="G179" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1+5</t>
         </is>
       </c>
       <c r="H179" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">~280x28</t>
+          <t xml:space="preserve">64px</t>
         </is>
       </c>
       <c r="I179" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">—</t>
+          <t xml:space="preserve">overlay</t>
         </is>
       </c>
       <c r="J179" t="inlineStr" s="6">
         <is>
           <t xml:space="preserve">P2</t>
-        </is>
-      </c>
-      <c r="K179" t="inlineStr" s="6">
-        <is>
-          <t xml:space="preserve">Canvas-drawn.</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">UI chrome</t>
+          <t xml:space="preserve">VFX &amp; animations</t>
         </is>
       </c>
       <c r="B180" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">Bars</t>
+          <t xml:space="preserve">Elemental</t>
         </is>
       </c>
       <c r="C180" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">Hero mini HP bar</t>
+          <t xml:space="preserve">Oil coat drip</t>
         </is>
       </c>
       <c r="D180" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">ui/minibar.png</t>
+          <t xml:space="preserve">fx/oil_0..2.png</t>
         </is>
       </c>
       <c r="E180" t="inlineStr" s="5">
@@ -11144,54 +11134,49 @@
       </c>
       <c r="F180" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">static</t>
+          <t xml:space="preserve">animation</t>
         </is>
       </c>
       <c r="G180" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H180" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">~60x8</t>
+          <t xml:space="preserve">48px</t>
         </is>
       </c>
       <c r="I180" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">—</t>
+          <t xml:space="preserve">overlay</t>
         </is>
       </c>
       <c r="J180" t="inlineStr" s="6">
         <is>
           <t xml:space="preserve">P3</t>
-        </is>
-      </c>
-      <c r="K180" t="inlineStr" s="6">
-        <is>
-          <t xml:space="preserve"/>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">UI chrome</t>
+          <t xml:space="preserve">VFX &amp; animations</t>
         </is>
       </c>
       <c r="B181" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">HUD</t>
+          <t xml:space="preserve">Elemental</t>
         </is>
       </c>
       <c r="C181" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">Ability button frame + cooldown sweep</t>
+          <t xml:space="preserve">Shock arc</t>
         </is>
       </c>
       <c r="D181" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">ui/abil_frame.png</t>
+          <t xml:space="preserve">fx/shock_0..3.png</t>
         </is>
       </c>
       <c r="E181" t="inlineStr" s="5">
@@ -11201,54 +11186,49 @@
       </c>
       <c r="F181" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">static</t>
+          <t xml:space="preserve">animation</t>
         </is>
       </c>
       <c r="G181" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="H181" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">96x96</t>
+          <t xml:space="preserve">64px</t>
         </is>
       </c>
       <c r="I181" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">radial sweep overlay</t>
+          <t xml:space="preserve">room-to-room</t>
         </is>
       </c>
       <c r="J181" t="inlineStr" s="6">
         <is>
           <t xml:space="preserve">P2</t>
-        </is>
-      </c>
-      <c r="K181" t="inlineStr" s="6">
-        <is>
-          <t xml:space="preserve">Emoji icon inside.</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">UI chrome</t>
+          <t xml:space="preserve">VFX &amp; animations</t>
         </is>
       </c>
       <c r="B182" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">HUD</t>
+          <t xml:space="preserve">Elemental</t>
         </is>
       </c>
       <c r="C182" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">Relic-bar slot frame</t>
+          <t xml:space="preserve">Poison bubbles</t>
         </is>
       </c>
       <c r="D182" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">ui/relic_slot.png</t>
+          <t xml:space="preserve">fx/poison_0..3.png</t>
         </is>
       </c>
       <c r="E182" t="inlineStr" s="5">
@@ -11258,54 +11238,49 @@
       </c>
       <c r="F182" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">static</t>
+          <t xml:space="preserve">animation</t>
         </is>
       </c>
       <c r="G182" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="H182" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">56x56</t>
+          <t xml:space="preserve">40px</t>
         </is>
       </c>
       <c r="I182" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">—</t>
+          <t xml:space="preserve">overlay</t>
         </is>
       </c>
       <c r="J182" t="inlineStr" s="6">
         <is>
           <t xml:space="preserve">P3</t>
-        </is>
-      </c>
-      <c r="K182" t="inlineStr" s="6">
-        <is>
-          <t xml:space="preserve"/>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">UI chrome</t>
+          <t xml:space="preserve">VFX &amp; animations</t>
         </is>
       </c>
       <c r="B183" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">HUD</t>
+          <t xml:space="preserve">Elemental</t>
         </is>
       </c>
       <c r="C183" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">Top bar backplate</t>
+          <t xml:space="preserve">Acid melt (armor)</t>
         </is>
       </c>
       <c r="D183" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">ui/topbar_9s.png</t>
+          <t xml:space="preserve">fx/acid_0..3.png</t>
         </is>
       </c>
       <c r="E183" t="inlineStr" s="5">
@@ -11315,54 +11290,49 @@
       </c>
       <c r="F183" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">9-slice</t>
+          <t xml:space="preserve">animation</t>
         </is>
       </c>
       <c r="G183" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="H183" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">—</t>
+          <t xml:space="preserve">48px</t>
         </is>
       </c>
       <c r="I183" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">—</t>
+          <t xml:space="preserve">overlay</t>
         </is>
       </c>
       <c r="J183" t="inlineStr" s="6">
         <is>
           <t xml:space="preserve">P3</t>
-        </is>
-      </c>
-      <c r="K183" t="inlineStr" s="6">
-        <is>
-          <t xml:space="preserve"/>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">UI chrome</t>
+          <t xml:space="preserve">VFX &amp; animations</t>
         </is>
       </c>
       <c r="B184" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">HUD</t>
+          <t xml:space="preserve">Elemental</t>
         </is>
       </c>
       <c r="C184" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">Zoom +/- , pause ☰, audio 🔊 button icons</t>
+          <t xml:space="preserve">Hex mark + detonation</t>
         </is>
       </c>
       <c r="D184" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">ui/ico_{zoom,pause,audio}.png</t>
+          <t xml:space="preserve">fx/mark.png + det_0..4.png</t>
         </is>
       </c>
       <c r="E184" t="inlineStr" s="5">
@@ -11372,54 +11342,49 @@
       </c>
       <c r="F184" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">static</t>
+          <t xml:space="preserve">animation</t>
         </is>
       </c>
       <c r="G184" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1+5</t>
         </is>
       </c>
       <c r="H184" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">64x64</t>
+          <t xml:space="preserve">64/96px</t>
         </is>
       </c>
       <c r="I184" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">—</t>
+          <t xml:space="preserve">target ring</t>
         </is>
       </c>
       <c r="J184" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">P3</t>
-        </is>
-      </c>
-      <c r="K184" t="inlineStr" s="6">
-        <is>
-          <t xml:space="preserve">Emoji/CSS today.</t>
+          <t xml:space="preserve">P2</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">UI chrome</t>
+          <t xml:space="preserve">VFX &amp; animations</t>
         </is>
       </c>
       <c r="B185" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">Banners</t>
+          <t xml:space="preserve">Combat</t>
         </is>
       </c>
       <c r="C185" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">Arrival banner ribbon (champion/rival/king)</t>
+          <t xml:space="preserve">Boss bolt projectile + impact (per-color tint)</t>
         </is>
       </c>
       <c r="D185" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">ui/banner_ribbon.png</t>
+          <t xml:space="preserve">fx/bolt.png + impact_0..3.png</t>
         </is>
       </c>
       <c r="E185" t="inlineStr" s="5">
@@ -11429,54 +11394,49 @@
       </c>
       <c r="F185" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">static</t>
+          <t xml:space="preserve">animation</t>
         </is>
       </c>
       <c r="G185" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1+4</t>
         </is>
       </c>
       <c r="H185" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">~900x160</t>
+          <t xml:space="preserve">32/64px</t>
         </is>
       </c>
       <c r="I185" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">center sweep</t>
+          <t xml:space="preserve">comet trail in engine</t>
         </is>
       </c>
       <c r="J185" t="inlineStr" s="6">
         <is>
           <t xml:space="preserve">P2</t>
-        </is>
-      </c>
-      <c r="K185" t="inlineStr" s="6">
-        <is>
-          <t xml:space="preserve">Canvas gradient banner today.</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">UI chrome</t>
+          <t xml:space="preserve">VFX &amp; animations</t>
         </is>
       </c>
       <c r="B186" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">Feedback</t>
+          <t xml:space="preserve">Combat</t>
         </is>
       </c>
       <c r="C186" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">Tutorial pulse / pointer hand</t>
+          <t xml:space="preserve">Hit spark / slash arc</t>
         </is>
       </c>
       <c r="D186" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">ui/pointer.png</t>
+          <t xml:space="preserve">fx/hit_0..2.png</t>
         </is>
       </c>
       <c r="E186" t="inlineStr" s="5">
@@ -11491,54 +11451,49 @@
       </c>
       <c r="G186" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H186" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">64x64</t>
+          <t xml:space="preserve">48px</t>
         </is>
       </c>
       <c r="I186" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">—</t>
+          <t xml:space="preserve">at strike point</t>
         </is>
       </c>
       <c r="J186" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">P3</t>
-        </is>
-      </c>
-      <c r="K186" t="inlineStr" s="6">
-        <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">P2</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">UI chrome</t>
+          <t xml:space="preserve">VFX &amp; animations</t>
         </is>
       </c>
       <c r="B187" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">Cursor</t>
+          <t xml:space="preserve">Combat</t>
         </is>
       </c>
       <c r="C187" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">Custom cursor + grab cursor</t>
+          <t xml:space="preserve">Shield bubble (paladin/champion)</t>
         </is>
       </c>
       <c r="D187" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">ui/cursor_*.png</t>
-        </is>
-      </c>
-      <c r="E187" t="inlineStr" s="4">
-        <is>
-          <t xml:space="preserve">MISSING</t>
+          <t xml:space="preserve">fx/shield.png</t>
+        </is>
+      </c>
+      <c r="E187" t="inlineStr" s="5">
+        <is>
+          <t xml:space="preserve">PROCEDURAL</t>
         </is>
       </c>
       <c r="F187" t="inlineStr" s="6">
@@ -11548,49 +11503,44 @@
       </c>
       <c r="G187" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H187" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">32x32</t>
+          <t xml:space="preserve">96px</t>
         </is>
       </c>
       <c r="I187" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">hotspot top-left</t>
+          <t xml:space="preserve">wraps sprite</t>
         </is>
       </c>
       <c r="J187" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">P3</t>
-        </is>
-      </c>
-      <c r="K187" t="inlineStr" s="6">
-        <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">P2</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">Icon sets</t>
+          <t xml:space="preserve">VFX &amp; animations</t>
         </is>
       </c>
       <c r="B188" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">Currencies</t>
+          <t xml:space="preserve">Combat</t>
         </is>
       </c>
       <c r="C188" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">Gold / Dread / Mana / HP icons</t>
+          <t xml:space="preserve">Heal sparkle / mana refill</t>
         </is>
       </c>
       <c r="D188" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">icons/cur_*.png</t>
+          <t xml:space="preserve">fx/heal_0..3.png</t>
         </is>
       </c>
       <c r="E188" t="inlineStr" s="5">
@@ -11600,7 +11550,7 @@
       </c>
       <c r="F188" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">static</t>
+          <t xml:space="preserve">animation</t>
         </is>
       </c>
       <c r="G188" t="inlineStr" s="6">
@@ -11610,44 +11560,39 @@
       </c>
       <c r="H188" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">64x64</t>
+          <t xml:space="preserve">48px</t>
         </is>
       </c>
       <c r="I188" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">—</t>
+          <t xml:space="preserve">rises</t>
         </is>
       </c>
       <c r="J188" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">P2</t>
-        </is>
-      </c>
-      <c r="K188" t="inlineStr" s="6">
-        <is>
-          <t xml:space="preserve">Emoji today (💰😈🔮❤️).</t>
+          <t xml:space="preserve">P3</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">Icon sets</t>
+          <t xml:space="preserve">VFX &amp; animations</t>
         </is>
       </c>
       <c r="B189" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">Currencies</t>
+          <t xml:space="preserve">Combat</t>
         </is>
       </c>
       <c r="C189" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">Rune points ◆ / lifetime kills ☠ / ascension crown</t>
+          <t xml:space="preserve">Overdrive shockwave ring</t>
         </is>
       </c>
       <c r="D189" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">icons/meta_*.png</t>
+          <t xml:space="preserve">fx/ring.png</t>
         </is>
       </c>
       <c r="E189" t="inlineStr" s="5">
@@ -11662,49 +11607,44 @@
       </c>
       <c r="G189" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H189" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">64x64</t>
+          <t xml:space="preserve">256px</t>
         </is>
       </c>
       <c r="I189" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">—</t>
+          <t xml:space="preserve">scales out</t>
         </is>
       </c>
       <c r="J189" t="inlineStr" s="6">
         <is>
           <t xml:space="preserve">P3</t>
-        </is>
-      </c>
-      <c r="K189" t="inlineStr" s="6">
-        <is>
-          <t xml:space="preserve"/>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">Icon sets</t>
+          <t xml:space="preserve">VFX &amp; animations</t>
         </is>
       </c>
       <c r="B190" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">Abilities</t>
+          <t xml:space="preserve">Economy</t>
         </is>
       </c>
       <c r="C190" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">14 boss-ability icons (slam, fire breath, bone bolt, curse, freeze, drain, dread, mend, quake, hellfire, mana siphon, devour, raise dead, entangle)</t>
+          <t xml:space="preserve">Gold coin burst / pickup</t>
         </is>
       </c>
       <c r="D190" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">icons/abil_*.png</t>
+          <t xml:space="preserve">fx/coin_0..3.png</t>
         </is>
       </c>
       <c r="E190" t="inlineStr" s="5">
@@ -11714,54 +11654,49 @@
       </c>
       <c r="F190" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">static</t>
+          <t xml:space="preserve">animation</t>
         </is>
       </c>
       <c r="G190" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">14</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="H190" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">96x96</t>
+          <t xml:space="preserve">24px</t>
         </is>
       </c>
       <c r="I190" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">—</t>
+          <t xml:space="preserve">arcs to counter</t>
         </is>
       </c>
       <c r="J190" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">P2</t>
-        </is>
-      </c>
-      <c r="K190" t="inlineStr" s="6">
-        <is>
-          <t xml:space="preserve">Emoji today; painted set = big HUD upgrade.</t>
+          <t xml:space="preserve">P3</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">Icon sets</t>
+          <t xml:space="preserve">VFX &amp; animations</t>
         </is>
       </c>
       <c r="B191" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">Relics</t>
+          <t xml:space="preserve">Build</t>
         </is>
       </c>
       <c r="C191" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">33 relic icons across 5 tiers (common/special/rare/epic/legendary)</t>
+          <t xml:space="preserve">Upgrade LVL burst</t>
         </is>
       </c>
       <c r="D191" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">icons/relic_*.png</t>
+          <t xml:space="preserve">fx/lvlup_0..4.png</t>
         </is>
       </c>
       <c r="E191" t="inlineStr" s="5">
@@ -11771,54 +11706,49 @@
       </c>
       <c r="F191" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">static</t>
+          <t xml:space="preserve">animation</t>
         </is>
       </c>
       <c r="G191" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">33</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="H191" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">96x96</t>
+          <t xml:space="preserve">96px</t>
         </is>
       </c>
       <c r="I191" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">tier border separate</t>
+          <t xml:space="preserve">over room</t>
         </is>
       </c>
       <c r="J191" t="inlineStr" s="6">
         <is>
           <t xml:space="preserve">P3</t>
-        </is>
-      </c>
-      <c r="K191" t="inlineStr" s="6">
-        <is>
-          <t xml:space="preserve">Emoji today.</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">Icon sets</t>
+          <t xml:space="preserve">VFX &amp; animations</t>
         </is>
       </c>
       <c r="B192" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">Traits</t>
+          <t xml:space="preserve">Build</t>
         </is>
       </c>
       <c r="C192" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">6 elite-trait icons (hardy/berserker/armored/swift/vampiric/zealot)</t>
+          <t xml:space="preserve">Fusion merge flash</t>
         </is>
       </c>
       <c r="D192" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">icons/trait_*.png</t>
+          <t xml:space="preserve">fx/fuse_0..4.png</t>
         </is>
       </c>
       <c r="E192" t="inlineStr" s="5">
@@ -11828,54 +11758,49 @@
       </c>
       <c r="F192" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">static</t>
+          <t xml:space="preserve">animation</t>
         </is>
       </c>
       <c r="G192" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="H192" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">48x48</t>
+          <t xml:space="preserve">128px</t>
         </is>
       </c>
       <c r="I192" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">—</t>
+          <t xml:space="preserve">two-into-one</t>
         </is>
       </c>
       <c r="J192" t="inlineStr" s="6">
         <is>
           <t xml:space="preserve">P3</t>
-        </is>
-      </c>
-      <c r="K192" t="inlineStr" s="6">
-        <is>
-          <t xml:space="preserve"/>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">Icon sets</t>
+          <t xml:space="preserve">VFX &amp; animations</t>
         </is>
       </c>
       <c r="B193" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">Edicts</t>
+          <t xml:space="preserve">Build</t>
         </is>
       </c>
       <c r="C193" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">7 edict icons</t>
+          <t xml:space="preserve">Demolish dust puff</t>
         </is>
       </c>
       <c r="D193" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">icons/edict_*.png</t>
+          <t xml:space="preserve">fx/dust_0..3.png</t>
         </is>
       </c>
       <c r="E193" t="inlineStr" s="5">
@@ -11885,17 +11810,17 @@
       </c>
       <c r="F193" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">static</t>
+          <t xml:space="preserve">animation</t>
         </is>
       </c>
       <c r="G193" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="H193" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">96x96</t>
+          <t xml:space="preserve">96px</t>
         </is>
       </c>
       <c r="I193" t="inlineStr" s="6">
@@ -11906,33 +11831,28 @@
       <c r="J193" t="inlineStr" s="6">
         <is>
           <t xml:space="preserve">P3</t>
-        </is>
-      </c>
-      <c r="K193" t="inlineStr" s="6">
-        <is>
-          <t xml:space="preserve"/>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">Icon sets</t>
+          <t xml:space="preserve">VFX &amp; animations</t>
         </is>
       </c>
       <c r="B194" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">Mandates</t>
+          <t xml:space="preserve">Ambience</t>
         </is>
       </c>
       <c r="C194" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">10 mandate icons</t>
+          <t xml:space="preserve">Torch flame loop (dungeon + town)</t>
         </is>
       </c>
       <c r="D194" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">icons/mandate_*.png</t>
+          <t xml:space="preserve">fx/torch_0..3.png</t>
         </is>
       </c>
       <c r="E194" t="inlineStr" s="5">
@@ -11942,17 +11862,17 @@
       </c>
       <c r="F194" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">static</t>
+          <t xml:space="preserve">animation</t>
         </is>
       </c>
       <c r="G194" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="H194" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">96x96</t>
+          <t xml:space="preserve">24px</t>
         </is>
       </c>
       <c r="I194" t="inlineStr" s="6">
@@ -11963,33 +11883,28 @@
       <c r="J194" t="inlineStr" s="6">
         <is>
           <t xml:space="preserve">P3</t>
-        </is>
-      </c>
-      <c r="K194" t="inlineStr" s="6">
-        <is>
-          <t xml:space="preserve"/>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">Icon sets</t>
+          <t xml:space="preserve">VFX &amp; animations</t>
         </is>
       </c>
       <c r="B195" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">Doctrines</t>
+          <t xml:space="preserve">Ambience</t>
         </is>
       </c>
       <c r="C195" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">6 boss-doctrine icons</t>
+          <t xml:space="preserve">Chimney smoke loop (smithy/foundry)</t>
         </is>
       </c>
       <c r="D195" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">icons/doc_*.png</t>
+          <t xml:space="preserve">fx/smoke_0..3.png</t>
         </is>
       </c>
       <c r="E195" t="inlineStr" s="5">
@@ -11999,59 +11914,54 @@
       </c>
       <c r="F195" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">static</t>
+          <t xml:space="preserve">animation</t>
         </is>
       </c>
       <c r="G195" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="H195" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">96x96</t>
+          <t xml:space="preserve">32px</t>
         </is>
       </c>
       <c r="I195" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">—</t>
+          <t xml:space="preserve">rises</t>
         </is>
       </c>
       <c r="J195" t="inlineStr" s="6">
         <is>
           <t xml:space="preserve">P3</t>
-        </is>
-      </c>
-      <c r="K195" t="inlineStr" s="6">
-        <is>
-          <t xml:space="preserve"/>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">Icon sets</t>
+          <t xml:space="preserve">VFX &amp; animations</t>
         </is>
       </c>
       <c r="B196" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">Runes</t>
+          <t xml:space="preserve">Ambience</t>
         </is>
       </c>
       <c r="C196" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">19 rune-tree node icons</t>
+          <t xml:space="preserve">Lightning flash overlay (arena storm)</t>
         </is>
       </c>
       <c r="D196" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">icons/rune_*.png</t>
-        </is>
-      </c>
-      <c r="E196" t="inlineStr" s="5">
-        <is>
-          <t xml:space="preserve">PROCEDURAL</t>
+          <t xml:space="preserve">fx/flash.png</t>
+        </is>
+      </c>
+      <c r="E196" t="inlineStr" s="4">
+        <is>
+          <t xml:space="preserve">MISSING</t>
         </is>
       </c>
       <c r="F196" t="inlineStr" s="6">
@@ -12061,49 +11971,44 @@
       </c>
       <c r="G196" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">19</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H196" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">96x96</t>
+          <t xml:space="preserve">screen</t>
         </is>
       </c>
       <c r="I196" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">—</t>
+          <t xml:space="preserve">additive</t>
         </is>
       </c>
       <c r="J196" t="inlineStr" s="6">
         <is>
           <t xml:space="preserve">P3</t>
-        </is>
-      </c>
-      <c r="K196" t="inlineStr" s="6">
-        <is>
-          <t xml:space="preserve">Rune page uses emoji nodes.</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">Icon sets</t>
+          <t xml:space="preserve">VFX &amp; animations</t>
         </is>
       </c>
       <c r="B197" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">Classes</t>
+          <t xml:space="preserve">Death</t>
         </is>
       </c>
       <c r="C197" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">4 hero-class icons (warrior/rogue/mage/cleric)</t>
+          <t xml:space="preserve">Hero death poof + soul wisp</t>
         </is>
       </c>
       <c r="D197" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">icons/cls_*.png</t>
+          <t xml:space="preserve">fx/death_0..4.png</t>
         </is>
       </c>
       <c r="E197" t="inlineStr" s="5">
@@ -12113,17 +12018,17 @@
       </c>
       <c r="F197" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">static</t>
+          <t xml:space="preserve">animation</t>
         </is>
       </c>
       <c r="G197" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="H197" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">64x64</t>
+          <t xml:space="preserve">64px</t>
         </is>
       </c>
       <c r="I197" t="inlineStr" s="6">
@@ -12133,1171 +12038,12 @@
       </c>
       <c r="J197" t="inlineStr" s="6">
         <is>
-          <t xml:space="preserve">P3</t>
-        </is>
-      </c>
-      <c r="K197" t="inlineStr" s="6">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-    </row>
-    <row r="198">
-      <c r="A198" t="inlineStr" s="6">
-        <is>
-          <t xml:space="preserve">Icon sets</t>
-        </is>
-      </c>
-      <c r="B198" t="inlineStr" s="6">
-        <is>
-          <t xml:space="preserve">Elements</t>
-        </is>
-      </c>
-      <c r="C198" t="inlineStr" s="6">
-        <is>
-          <t xml:space="preserve">7 element icons (phys/fire/ice/oil/shock/poison/acid)</t>
-        </is>
-      </c>
-      <c r="D198" t="inlineStr" s="6">
-        <is>
-          <t xml:space="preserve">icons/elem_*.png</t>
-        </is>
-      </c>
-      <c r="E198" t="inlineStr" s="5">
-        <is>
-          <t xml:space="preserve">PROCEDURAL</t>
-        </is>
-      </c>
-      <c r="F198" t="inlineStr" s="6">
-        <is>
-          <t xml:space="preserve">static</t>
-        </is>
-      </c>
-      <c r="G198" t="inlineStr" s="6">
-        <is>
-          <t xml:space="preserve">7</t>
-        </is>
-      </c>
-      <c r="H198" t="inlineStr" s="6">
-        <is>
-          <t xml:space="preserve">48x48</t>
-        </is>
-      </c>
-      <c r="I198" t="inlineStr" s="6">
-        <is>
-          <t xml:space="preserve">—</t>
-        </is>
-      </c>
-      <c r="J198" t="inlineStr" s="6">
-        <is>
           <t xml:space="preserve">P2</t>
         </is>
       </c>
-      <c r="K198" t="inlineStr" s="6">
-        <is>
-          <t xml:space="preserve">Used in tooltips &amp; codex.</t>
-        </is>
-      </c>
-    </row>
-    <row r="199">
-      <c r="A199" t="inlineStr" s="6">
-        <is>
-          <t xml:space="preserve">Icon sets</t>
-        </is>
-      </c>
-      <c r="B199" t="inlineStr" s="6">
-        <is>
-          <t xml:space="preserve">Reactions</t>
-        </is>
-      </c>
-      <c r="C199" t="inlineStr" s="6">
-        <is>
-          <t xml:space="preserve">Reaction icons (shatter/ignite/detonate/conduct/melt)</t>
-        </is>
-      </c>
-      <c r="D199" t="inlineStr" s="6">
-        <is>
-          <t xml:space="preserve">icons/react_*.png</t>
-        </is>
-      </c>
-      <c r="E199" t="inlineStr" s="5">
-        <is>
-          <t xml:space="preserve">PROCEDURAL</t>
-        </is>
-      </c>
-      <c r="F199" t="inlineStr" s="6">
-        <is>
-          <t xml:space="preserve">static</t>
-        </is>
-      </c>
-      <c r="G199" t="inlineStr" s="6">
-        <is>
-          <t xml:space="preserve">5</t>
-        </is>
-      </c>
-      <c r="H199" t="inlineStr" s="6">
-        <is>
-          <t xml:space="preserve">48x48</t>
-        </is>
-      </c>
-      <c r="I199" t="inlineStr" s="6">
-        <is>
-          <t xml:space="preserve">—</t>
-        </is>
-      </c>
-      <c r="J199" t="inlineStr" s="6">
-        <is>
-          <t xml:space="preserve">P3</t>
-        </is>
-      </c>
-      <c r="K199" t="inlineStr" s="6">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-    </row>
-    <row r="200">
-      <c r="A200" t="inlineStr" s="6">
-        <is>
-          <t xml:space="preserve">VFX &amp; animations</t>
-        </is>
-      </c>
-      <c r="B200" t="inlineStr" s="6">
-        <is>
-          <t xml:space="preserve">Elemental</t>
-        </is>
-      </c>
-      <c r="C200" t="inlineStr" s="6">
-        <is>
-          <t xml:space="preserve">Burn flame loop (on hero)</t>
-        </is>
-      </c>
-      <c r="D200" t="inlineStr" s="6">
-        <is>
-          <t xml:space="preserve">fx/burn_0..3.png</t>
-        </is>
-      </c>
-      <c r="E200" t="inlineStr" s="5">
-        <is>
-          <t xml:space="preserve">PROCEDURAL</t>
-        </is>
-      </c>
-      <c r="F200" t="inlineStr" s="6">
-        <is>
-          <t xml:space="preserve">animation</t>
-        </is>
-      </c>
-      <c r="G200" t="inlineStr" s="6">
-        <is>
-          <t xml:space="preserve">4</t>
-        </is>
-      </c>
-      <c r="H200" t="inlineStr" s="6">
-        <is>
-          <t xml:space="preserve">48px</t>
-        </is>
-      </c>
-      <c r="I200" t="inlineStr" s="6">
-        <is>
-          <t xml:space="preserve">overlay</t>
-        </is>
-      </c>
-      <c r="J200" t="inlineStr" s="6">
-        <is>
-          <t xml:space="preserve">P2</t>
-        </is>
-      </c>
-    </row>
-    <row r="201">
-      <c r="A201" t="inlineStr" s="6">
-        <is>
-          <t xml:space="preserve">VFX &amp; animations</t>
-        </is>
-      </c>
-      <c r="B201" t="inlineStr" s="6">
-        <is>
-          <t xml:space="preserve">Elemental</t>
-        </is>
-      </c>
-      <c r="C201" t="inlineStr" s="6">
-        <is>
-          <t xml:space="preserve">Freeze block + shatter burst</t>
-        </is>
-      </c>
-      <c r="D201" t="inlineStr" s="6">
-        <is>
-          <t xml:space="preserve">fx/freeze.png + shatter_0..4.png</t>
-        </is>
-      </c>
-      <c r="E201" t="inlineStr" s="5">
-        <is>
-          <t xml:space="preserve">PROCEDURAL</t>
-        </is>
-      </c>
-      <c r="F201" t="inlineStr" s="6">
-        <is>
-          <t xml:space="preserve">animation</t>
-        </is>
-      </c>
-      <c r="G201" t="inlineStr" s="6">
-        <is>
-          <t xml:space="preserve">1+5</t>
-        </is>
-      </c>
-      <c r="H201" t="inlineStr" s="6">
-        <is>
-          <t xml:space="preserve">64px</t>
-        </is>
-      </c>
-      <c r="I201" t="inlineStr" s="6">
-        <is>
-          <t xml:space="preserve">overlay</t>
-        </is>
-      </c>
-      <c r="J201" t="inlineStr" s="6">
-        <is>
-          <t xml:space="preserve">P2</t>
-        </is>
-      </c>
-    </row>
-    <row r="202">
-      <c r="A202" t="inlineStr" s="6">
-        <is>
-          <t xml:space="preserve">VFX &amp; animations</t>
-        </is>
-      </c>
-      <c r="B202" t="inlineStr" s="6">
-        <is>
-          <t xml:space="preserve">Elemental</t>
-        </is>
-      </c>
-      <c r="C202" t="inlineStr" s="6">
-        <is>
-          <t xml:space="preserve">Oil coat drip</t>
-        </is>
-      </c>
-      <c r="D202" t="inlineStr" s="6">
-        <is>
-          <t xml:space="preserve">fx/oil_0..2.png</t>
-        </is>
-      </c>
-      <c r="E202" t="inlineStr" s="5">
-        <is>
-          <t xml:space="preserve">PROCEDURAL</t>
-        </is>
-      </c>
-      <c r="F202" t="inlineStr" s="6">
-        <is>
-          <t xml:space="preserve">animation</t>
-        </is>
-      </c>
-      <c r="G202" t="inlineStr" s="6">
-        <is>
-          <t xml:space="preserve">3</t>
-        </is>
-      </c>
-      <c r="H202" t="inlineStr" s="6">
-        <is>
-          <t xml:space="preserve">48px</t>
-        </is>
-      </c>
-      <c r="I202" t="inlineStr" s="6">
-        <is>
-          <t xml:space="preserve">overlay</t>
-        </is>
-      </c>
-      <c r="J202" t="inlineStr" s="6">
-        <is>
-          <t xml:space="preserve">P3</t>
-        </is>
-      </c>
-    </row>
-    <row r="203">
-      <c r="A203" t="inlineStr" s="6">
-        <is>
-          <t xml:space="preserve">VFX &amp; animations</t>
-        </is>
-      </c>
-      <c r="B203" t="inlineStr" s="6">
-        <is>
-          <t xml:space="preserve">Elemental</t>
-        </is>
-      </c>
-      <c r="C203" t="inlineStr" s="6">
-        <is>
-          <t xml:space="preserve">Shock arc</t>
-        </is>
-      </c>
-      <c r="D203" t="inlineStr" s="6">
-        <is>
-          <t xml:space="preserve">fx/shock_0..3.png</t>
-        </is>
-      </c>
-      <c r="E203" t="inlineStr" s="5">
-        <is>
-          <t xml:space="preserve">PROCEDURAL</t>
-        </is>
-      </c>
-      <c r="F203" t="inlineStr" s="6">
-        <is>
-          <t xml:space="preserve">animation</t>
-        </is>
-      </c>
-      <c r="G203" t="inlineStr" s="6">
-        <is>
-          <t xml:space="preserve">4</t>
-        </is>
-      </c>
-      <c r="H203" t="inlineStr" s="6">
-        <is>
-          <t xml:space="preserve">64px</t>
-        </is>
-      </c>
-      <c r="I203" t="inlineStr" s="6">
-        <is>
-          <t xml:space="preserve">room-to-room</t>
-        </is>
-      </c>
-      <c r="J203" t="inlineStr" s="6">
-        <is>
-          <t xml:space="preserve">P2</t>
-        </is>
-      </c>
-    </row>
-    <row r="204">
-      <c r="A204" t="inlineStr" s="6">
-        <is>
-          <t xml:space="preserve">VFX &amp; animations</t>
-        </is>
-      </c>
-      <c r="B204" t="inlineStr" s="6">
-        <is>
-          <t xml:space="preserve">Elemental</t>
-        </is>
-      </c>
-      <c r="C204" t="inlineStr" s="6">
-        <is>
-          <t xml:space="preserve">Poison bubbles</t>
-        </is>
-      </c>
-      <c r="D204" t="inlineStr" s="6">
-        <is>
-          <t xml:space="preserve">fx/poison_0..3.png</t>
-        </is>
-      </c>
-      <c r="E204" t="inlineStr" s="5">
-        <is>
-          <t xml:space="preserve">PROCEDURAL</t>
-        </is>
-      </c>
-      <c r="F204" t="inlineStr" s="6">
-        <is>
-          <t xml:space="preserve">animation</t>
-        </is>
-      </c>
-      <c r="G204" t="inlineStr" s="6">
-        <is>
-          <t xml:space="preserve">4</t>
-        </is>
-      </c>
-      <c r="H204" t="inlineStr" s="6">
-        <is>
-          <t xml:space="preserve">40px</t>
-        </is>
-      </c>
-      <c r="I204" t="inlineStr" s="6">
-        <is>
-          <t xml:space="preserve">overlay</t>
-        </is>
-      </c>
-      <c r="J204" t="inlineStr" s="6">
-        <is>
-          <t xml:space="preserve">P3</t>
-        </is>
-      </c>
-    </row>
-    <row r="205">
-      <c r="A205" t="inlineStr" s="6">
-        <is>
-          <t xml:space="preserve">VFX &amp; animations</t>
-        </is>
-      </c>
-      <c r="B205" t="inlineStr" s="6">
-        <is>
-          <t xml:space="preserve">Elemental</t>
-        </is>
-      </c>
-      <c r="C205" t="inlineStr" s="6">
-        <is>
-          <t xml:space="preserve">Acid melt (armor)</t>
-        </is>
-      </c>
-      <c r="D205" t="inlineStr" s="6">
-        <is>
-          <t xml:space="preserve">fx/acid_0..3.png</t>
-        </is>
-      </c>
-      <c r="E205" t="inlineStr" s="5">
-        <is>
-          <t xml:space="preserve">PROCEDURAL</t>
-        </is>
-      </c>
-      <c r="F205" t="inlineStr" s="6">
-        <is>
-          <t xml:space="preserve">animation</t>
-        </is>
-      </c>
-      <c r="G205" t="inlineStr" s="6">
-        <is>
-          <t xml:space="preserve">4</t>
-        </is>
-      </c>
-      <c r="H205" t="inlineStr" s="6">
-        <is>
-          <t xml:space="preserve">48px</t>
-        </is>
-      </c>
-      <c r="I205" t="inlineStr" s="6">
-        <is>
-          <t xml:space="preserve">overlay</t>
-        </is>
-      </c>
-      <c r="J205" t="inlineStr" s="6">
-        <is>
-          <t xml:space="preserve">P3</t>
-        </is>
-      </c>
-    </row>
-    <row r="206">
-      <c r="A206" t="inlineStr" s="6">
-        <is>
-          <t xml:space="preserve">VFX &amp; animations</t>
-        </is>
-      </c>
-      <c r="B206" t="inlineStr" s="6">
-        <is>
-          <t xml:space="preserve">Elemental</t>
-        </is>
-      </c>
-      <c r="C206" t="inlineStr" s="6">
-        <is>
-          <t xml:space="preserve">Hex mark + detonation</t>
-        </is>
-      </c>
-      <c r="D206" t="inlineStr" s="6">
-        <is>
-          <t xml:space="preserve">fx/mark.png + det_0..4.png</t>
-        </is>
-      </c>
-      <c r="E206" t="inlineStr" s="5">
-        <is>
-          <t xml:space="preserve">PROCEDURAL</t>
-        </is>
-      </c>
-      <c r="F206" t="inlineStr" s="6">
-        <is>
-          <t xml:space="preserve">animation</t>
-        </is>
-      </c>
-      <c r="G206" t="inlineStr" s="6">
-        <is>
-          <t xml:space="preserve">1+5</t>
-        </is>
-      </c>
-      <c r="H206" t="inlineStr" s="6">
-        <is>
-          <t xml:space="preserve">64/96px</t>
-        </is>
-      </c>
-      <c r="I206" t="inlineStr" s="6">
-        <is>
-          <t xml:space="preserve">target ring</t>
-        </is>
-      </c>
-      <c r="J206" t="inlineStr" s="6">
-        <is>
-          <t xml:space="preserve">P2</t>
-        </is>
-      </c>
-    </row>
-    <row r="207">
-      <c r="A207" t="inlineStr" s="6">
-        <is>
-          <t xml:space="preserve">VFX &amp; animations</t>
-        </is>
-      </c>
-      <c r="B207" t="inlineStr" s="6">
-        <is>
-          <t xml:space="preserve">Combat</t>
-        </is>
-      </c>
-      <c r="C207" t="inlineStr" s="6">
-        <is>
-          <t xml:space="preserve">Boss bolt projectile + impact (per-color tint)</t>
-        </is>
-      </c>
-      <c r="D207" t="inlineStr" s="6">
-        <is>
-          <t xml:space="preserve">fx/bolt.png + impact_0..3.png</t>
-        </is>
-      </c>
-      <c r="E207" t="inlineStr" s="5">
-        <is>
-          <t xml:space="preserve">PROCEDURAL</t>
-        </is>
-      </c>
-      <c r="F207" t="inlineStr" s="6">
-        <is>
-          <t xml:space="preserve">animation</t>
-        </is>
-      </c>
-      <c r="G207" t="inlineStr" s="6">
-        <is>
-          <t xml:space="preserve">1+4</t>
-        </is>
-      </c>
-      <c r="H207" t="inlineStr" s="6">
-        <is>
-          <t xml:space="preserve">32/64px</t>
-        </is>
-      </c>
-      <c r="I207" t="inlineStr" s="6">
-        <is>
-          <t xml:space="preserve">comet trail in engine</t>
-        </is>
-      </c>
-      <c r="J207" t="inlineStr" s="6">
-        <is>
-          <t xml:space="preserve">P2</t>
-        </is>
-      </c>
-    </row>
-    <row r="208">
-      <c r="A208" t="inlineStr" s="6">
-        <is>
-          <t xml:space="preserve">VFX &amp; animations</t>
-        </is>
-      </c>
-      <c r="B208" t="inlineStr" s="6">
-        <is>
-          <t xml:space="preserve">Combat</t>
-        </is>
-      </c>
-      <c r="C208" t="inlineStr" s="6">
-        <is>
-          <t xml:space="preserve">Hit spark / slash arc</t>
-        </is>
-      </c>
-      <c r="D208" t="inlineStr" s="6">
-        <is>
-          <t xml:space="preserve">fx/hit_0..2.png</t>
-        </is>
-      </c>
-      <c r="E208" t="inlineStr" s="5">
-        <is>
-          <t xml:space="preserve">PROCEDURAL</t>
-        </is>
-      </c>
-      <c r="F208" t="inlineStr" s="6">
-        <is>
-          <t xml:space="preserve">animation</t>
-        </is>
-      </c>
-      <c r="G208" t="inlineStr" s="6">
-        <is>
-          <t xml:space="preserve">3</t>
-        </is>
-      </c>
-      <c r="H208" t="inlineStr" s="6">
-        <is>
-          <t xml:space="preserve">48px</t>
-        </is>
-      </c>
-      <c r="I208" t="inlineStr" s="6">
-        <is>
-          <t xml:space="preserve">at strike point</t>
-        </is>
-      </c>
-      <c r="J208" t="inlineStr" s="6">
-        <is>
-          <t xml:space="preserve">P2</t>
-        </is>
-      </c>
-    </row>
-    <row r="209">
-      <c r="A209" t="inlineStr" s="6">
-        <is>
-          <t xml:space="preserve">VFX &amp; animations</t>
-        </is>
-      </c>
-      <c r="B209" t="inlineStr" s="6">
-        <is>
-          <t xml:space="preserve">Combat</t>
-        </is>
-      </c>
-      <c r="C209" t="inlineStr" s="6">
-        <is>
-          <t xml:space="preserve">Shield bubble (paladin/champion)</t>
-        </is>
-      </c>
-      <c r="D209" t="inlineStr" s="6">
-        <is>
-          <t xml:space="preserve">fx/shield.png</t>
-        </is>
-      </c>
-      <c r="E209" t="inlineStr" s="5">
-        <is>
-          <t xml:space="preserve">PROCEDURAL</t>
-        </is>
-      </c>
-      <c r="F209" t="inlineStr" s="6">
-        <is>
-          <t xml:space="preserve">static</t>
-        </is>
-      </c>
-      <c r="G209" t="inlineStr" s="6">
-        <is>
-          <t xml:space="preserve">1</t>
-        </is>
-      </c>
-      <c r="H209" t="inlineStr" s="6">
-        <is>
-          <t xml:space="preserve">96px</t>
-        </is>
-      </c>
-      <c r="I209" t="inlineStr" s="6">
-        <is>
-          <t xml:space="preserve">wraps sprite</t>
-        </is>
-      </c>
-      <c r="J209" t="inlineStr" s="6">
-        <is>
-          <t xml:space="preserve">P2</t>
-        </is>
-      </c>
-    </row>
-    <row r="210">
-      <c r="A210" t="inlineStr" s="6">
-        <is>
-          <t xml:space="preserve">VFX &amp; animations</t>
-        </is>
-      </c>
-      <c r="B210" t="inlineStr" s="6">
-        <is>
-          <t xml:space="preserve">Combat</t>
-        </is>
-      </c>
-      <c r="C210" t="inlineStr" s="6">
-        <is>
-          <t xml:space="preserve">Heal sparkle / mana refill</t>
-        </is>
-      </c>
-      <c r="D210" t="inlineStr" s="6">
-        <is>
-          <t xml:space="preserve">fx/heal_0..3.png</t>
-        </is>
-      </c>
-      <c r="E210" t="inlineStr" s="5">
-        <is>
-          <t xml:space="preserve">PROCEDURAL</t>
-        </is>
-      </c>
-      <c r="F210" t="inlineStr" s="6">
-        <is>
-          <t xml:space="preserve">animation</t>
-        </is>
-      </c>
-      <c r="G210" t="inlineStr" s="6">
-        <is>
-          <t xml:space="preserve">4</t>
-        </is>
-      </c>
-      <c r="H210" t="inlineStr" s="6">
-        <is>
-          <t xml:space="preserve">48px</t>
-        </is>
-      </c>
-      <c r="I210" t="inlineStr" s="6">
-        <is>
-          <t xml:space="preserve">rises</t>
-        </is>
-      </c>
-      <c r="J210" t="inlineStr" s="6">
-        <is>
-          <t xml:space="preserve">P3</t>
-        </is>
-      </c>
-    </row>
-    <row r="211">
-      <c r="A211" t="inlineStr" s="6">
-        <is>
-          <t xml:space="preserve">VFX &amp; animations</t>
-        </is>
-      </c>
-      <c r="B211" t="inlineStr" s="6">
-        <is>
-          <t xml:space="preserve">Combat</t>
-        </is>
-      </c>
-      <c r="C211" t="inlineStr" s="6">
-        <is>
-          <t xml:space="preserve">Overdrive shockwave ring</t>
-        </is>
-      </c>
-      <c r="D211" t="inlineStr" s="6">
-        <is>
-          <t xml:space="preserve">fx/ring.png</t>
-        </is>
-      </c>
-      <c r="E211" t="inlineStr" s="5">
-        <is>
-          <t xml:space="preserve">PROCEDURAL</t>
-        </is>
-      </c>
-      <c r="F211" t="inlineStr" s="6">
-        <is>
-          <t xml:space="preserve">static</t>
-        </is>
-      </c>
-      <c r="G211" t="inlineStr" s="6">
-        <is>
-          <t xml:space="preserve">1</t>
-        </is>
-      </c>
-      <c r="H211" t="inlineStr" s="6">
-        <is>
-          <t xml:space="preserve">256px</t>
-        </is>
-      </c>
-      <c r="I211" t="inlineStr" s="6">
-        <is>
-          <t xml:space="preserve">scales out</t>
-        </is>
-      </c>
-      <c r="J211" t="inlineStr" s="6">
-        <is>
-          <t xml:space="preserve">P3</t>
-        </is>
-      </c>
-    </row>
-    <row r="212">
-      <c r="A212" t="inlineStr" s="6">
-        <is>
-          <t xml:space="preserve">VFX &amp; animations</t>
-        </is>
-      </c>
-      <c r="B212" t="inlineStr" s="6">
-        <is>
-          <t xml:space="preserve">Economy</t>
-        </is>
-      </c>
-      <c r="C212" t="inlineStr" s="6">
-        <is>
-          <t xml:space="preserve">Gold coin burst / pickup</t>
-        </is>
-      </c>
-      <c r="D212" t="inlineStr" s="6">
-        <is>
-          <t xml:space="preserve">fx/coin_0..3.png</t>
-        </is>
-      </c>
-      <c r="E212" t="inlineStr" s="5">
-        <is>
-          <t xml:space="preserve">PROCEDURAL</t>
-        </is>
-      </c>
-      <c r="F212" t="inlineStr" s="6">
-        <is>
-          <t xml:space="preserve">animation</t>
-        </is>
-      </c>
-      <c r="G212" t="inlineStr" s="6">
-        <is>
-          <t xml:space="preserve">4</t>
-        </is>
-      </c>
-      <c r="H212" t="inlineStr" s="6">
-        <is>
-          <t xml:space="preserve">24px</t>
-        </is>
-      </c>
-      <c r="I212" t="inlineStr" s="6">
-        <is>
-          <t xml:space="preserve">arcs to counter</t>
-        </is>
-      </c>
-      <c r="J212" t="inlineStr" s="6">
-        <is>
-          <t xml:space="preserve">P3</t>
-        </is>
-      </c>
-    </row>
-    <row r="213">
-      <c r="A213" t="inlineStr" s="6">
-        <is>
-          <t xml:space="preserve">VFX &amp; animations</t>
-        </is>
-      </c>
-      <c r="B213" t="inlineStr" s="6">
-        <is>
-          <t xml:space="preserve">Build</t>
-        </is>
-      </c>
-      <c r="C213" t="inlineStr" s="6">
-        <is>
-          <t xml:space="preserve">Upgrade LVL burst</t>
-        </is>
-      </c>
-      <c r="D213" t="inlineStr" s="6">
-        <is>
-          <t xml:space="preserve">fx/lvlup_0..4.png</t>
-        </is>
-      </c>
-      <c r="E213" t="inlineStr" s="5">
-        <is>
-          <t xml:space="preserve">PROCEDURAL</t>
-        </is>
-      </c>
-      <c r="F213" t="inlineStr" s="6">
-        <is>
-          <t xml:space="preserve">animation</t>
-        </is>
-      </c>
-      <c r="G213" t="inlineStr" s="6">
-        <is>
-          <t xml:space="preserve">5</t>
-        </is>
-      </c>
-      <c r="H213" t="inlineStr" s="6">
-        <is>
-          <t xml:space="preserve">96px</t>
-        </is>
-      </c>
-      <c r="I213" t="inlineStr" s="6">
-        <is>
-          <t xml:space="preserve">over room</t>
-        </is>
-      </c>
-      <c r="J213" t="inlineStr" s="6">
-        <is>
-          <t xml:space="preserve">P3</t>
-        </is>
-      </c>
-    </row>
-    <row r="214">
-      <c r="A214" t="inlineStr" s="6">
-        <is>
-          <t xml:space="preserve">VFX &amp; animations</t>
-        </is>
-      </c>
-      <c r="B214" t="inlineStr" s="6">
-        <is>
-          <t xml:space="preserve">Build</t>
-        </is>
-      </c>
-      <c r="C214" t="inlineStr" s="6">
-        <is>
-          <t xml:space="preserve">Fusion merge flash</t>
-        </is>
-      </c>
-      <c r="D214" t="inlineStr" s="6">
-        <is>
-          <t xml:space="preserve">fx/fuse_0..4.png</t>
-        </is>
-      </c>
-      <c r="E214" t="inlineStr" s="5">
-        <is>
-          <t xml:space="preserve">PROCEDURAL</t>
-        </is>
-      </c>
-      <c r="F214" t="inlineStr" s="6">
-        <is>
-          <t xml:space="preserve">animation</t>
-        </is>
-      </c>
-      <c r="G214" t="inlineStr" s="6">
-        <is>
-          <t xml:space="preserve">5</t>
-        </is>
-      </c>
-      <c r="H214" t="inlineStr" s="6">
-        <is>
-          <t xml:space="preserve">128px</t>
-        </is>
-      </c>
-      <c r="I214" t="inlineStr" s="6">
-        <is>
-          <t xml:space="preserve">two-into-one</t>
-        </is>
-      </c>
-      <c r="J214" t="inlineStr" s="6">
-        <is>
-          <t xml:space="preserve">P3</t>
-        </is>
-      </c>
-    </row>
-    <row r="215">
-      <c r="A215" t="inlineStr" s="6">
-        <is>
-          <t xml:space="preserve">VFX &amp; animations</t>
-        </is>
-      </c>
-      <c r="B215" t="inlineStr" s="6">
-        <is>
-          <t xml:space="preserve">Build</t>
-        </is>
-      </c>
-      <c r="C215" t="inlineStr" s="6">
-        <is>
-          <t xml:space="preserve">Demolish dust puff</t>
-        </is>
-      </c>
-      <c r="D215" t="inlineStr" s="6">
-        <is>
-          <t xml:space="preserve">fx/dust_0..3.png</t>
-        </is>
-      </c>
-      <c r="E215" t="inlineStr" s="5">
-        <is>
-          <t xml:space="preserve">PROCEDURAL</t>
-        </is>
-      </c>
-      <c r="F215" t="inlineStr" s="6">
-        <is>
-          <t xml:space="preserve">animation</t>
-        </is>
-      </c>
-      <c r="G215" t="inlineStr" s="6">
-        <is>
-          <t xml:space="preserve">4</t>
-        </is>
-      </c>
-      <c r="H215" t="inlineStr" s="6">
-        <is>
-          <t xml:space="preserve">96px</t>
-        </is>
-      </c>
-      <c r="I215" t="inlineStr" s="6">
-        <is>
-          <t xml:space="preserve">—</t>
-        </is>
-      </c>
-      <c r="J215" t="inlineStr" s="6">
-        <is>
-          <t xml:space="preserve">P3</t>
-        </is>
-      </c>
-    </row>
-    <row r="216">
-      <c r="A216" t="inlineStr" s="6">
-        <is>
-          <t xml:space="preserve">VFX &amp; animations</t>
-        </is>
-      </c>
-      <c r="B216" t="inlineStr" s="6">
-        <is>
-          <t xml:space="preserve">Ambience</t>
-        </is>
-      </c>
-      <c r="C216" t="inlineStr" s="6">
-        <is>
-          <t xml:space="preserve">Torch flame loop (dungeon + town)</t>
-        </is>
-      </c>
-      <c r="D216" t="inlineStr" s="6">
-        <is>
-          <t xml:space="preserve">fx/torch_0..3.png</t>
-        </is>
-      </c>
-      <c r="E216" t="inlineStr" s="5">
-        <is>
-          <t xml:space="preserve">PROCEDURAL</t>
-        </is>
-      </c>
-      <c r="F216" t="inlineStr" s="6">
-        <is>
-          <t xml:space="preserve">animation</t>
-        </is>
-      </c>
-      <c r="G216" t="inlineStr" s="6">
-        <is>
-          <t xml:space="preserve">4</t>
-        </is>
-      </c>
-      <c r="H216" t="inlineStr" s="6">
-        <is>
-          <t xml:space="preserve">24px</t>
-        </is>
-      </c>
-      <c r="I216" t="inlineStr" s="6">
-        <is>
-          <t xml:space="preserve">—</t>
-        </is>
-      </c>
-      <c r="J216" t="inlineStr" s="6">
-        <is>
-          <t xml:space="preserve">P3</t>
-        </is>
-      </c>
-    </row>
-    <row r="217">
-      <c r="A217" t="inlineStr" s="6">
-        <is>
-          <t xml:space="preserve">VFX &amp; animations</t>
-        </is>
-      </c>
-      <c r="B217" t="inlineStr" s="6">
-        <is>
-          <t xml:space="preserve">Ambience</t>
-        </is>
-      </c>
-      <c r="C217" t="inlineStr" s="6">
-        <is>
-          <t xml:space="preserve">Chimney smoke loop (smithy/foundry)</t>
-        </is>
-      </c>
-      <c r="D217" t="inlineStr" s="6">
-        <is>
-          <t xml:space="preserve">fx/smoke_0..3.png</t>
-        </is>
-      </c>
-      <c r="E217" t="inlineStr" s="5">
-        <is>
-          <t xml:space="preserve">PROCEDURAL</t>
-        </is>
-      </c>
-      <c r="F217" t="inlineStr" s="6">
-        <is>
-          <t xml:space="preserve">animation</t>
-        </is>
-      </c>
-      <c r="G217" t="inlineStr" s="6">
-        <is>
-          <t xml:space="preserve">4</t>
-        </is>
-      </c>
-      <c r="H217" t="inlineStr" s="6">
-        <is>
-          <t xml:space="preserve">32px</t>
-        </is>
-      </c>
-      <c r="I217" t="inlineStr" s="6">
-        <is>
-          <t xml:space="preserve">rises</t>
-        </is>
-      </c>
-      <c r="J217" t="inlineStr" s="6">
-        <is>
-          <t xml:space="preserve">P3</t>
-        </is>
-      </c>
-    </row>
-    <row r="218">
-      <c r="A218" t="inlineStr" s="6">
-        <is>
-          <t xml:space="preserve">VFX &amp; animations</t>
-        </is>
-      </c>
-      <c r="B218" t="inlineStr" s="6">
-        <is>
-          <t xml:space="preserve">Ambience</t>
-        </is>
-      </c>
-      <c r="C218" t="inlineStr" s="6">
-        <is>
-          <t xml:space="preserve">Lightning flash overlay (arena storm)</t>
-        </is>
-      </c>
-      <c r="D218" t="inlineStr" s="6">
-        <is>
-          <t xml:space="preserve">fx/flash.png</t>
-        </is>
-      </c>
-      <c r="E218" t="inlineStr" s="4">
-        <is>
-          <t xml:space="preserve">MISSING</t>
-        </is>
-      </c>
-      <c r="F218" t="inlineStr" s="6">
-        <is>
-          <t xml:space="preserve">static</t>
-        </is>
-      </c>
-      <c r="G218" t="inlineStr" s="6">
-        <is>
-          <t xml:space="preserve">1</t>
-        </is>
-      </c>
-      <c r="H218" t="inlineStr" s="6">
-        <is>
-          <t xml:space="preserve">screen</t>
-        </is>
-      </c>
-      <c r="I218" t="inlineStr" s="6">
-        <is>
-          <t xml:space="preserve">additive</t>
-        </is>
-      </c>
-      <c r="J218" t="inlineStr" s="6">
-        <is>
-          <t xml:space="preserve">P3</t>
-        </is>
-      </c>
-    </row>
-    <row r="219">
-      <c r="A219" t="inlineStr" s="6">
-        <is>
-          <t xml:space="preserve">VFX &amp; animations</t>
-        </is>
-      </c>
-      <c r="B219" t="inlineStr" s="6">
-        <is>
-          <t xml:space="preserve">Death</t>
-        </is>
-      </c>
-      <c r="C219" t="inlineStr" s="6">
-        <is>
-          <t xml:space="preserve">Hero death poof + soul wisp</t>
-        </is>
-      </c>
-      <c r="D219" t="inlineStr" s="6">
-        <is>
-          <t xml:space="preserve">fx/death_0..4.png</t>
-        </is>
-      </c>
-      <c r="E219" t="inlineStr" s="5">
-        <is>
-          <t xml:space="preserve">PROCEDURAL</t>
-        </is>
-      </c>
-      <c r="F219" t="inlineStr" s="6">
-        <is>
-          <t xml:space="preserve">animation</t>
-        </is>
-      </c>
-      <c r="G219" t="inlineStr" s="6">
-        <is>
-          <t xml:space="preserve">5</t>
-        </is>
-      </c>
-      <c r="H219" t="inlineStr" s="6">
-        <is>
-          <t xml:space="preserve">64px</t>
-        </is>
-      </c>
-      <c r="I219" t="inlineStr" s="6">
-        <is>
-          <t xml:space="preserve">—</t>
-        </is>
-      </c>
-      <c r="J219" t="inlineStr" s="6">
-        <is>
-          <t xml:space="preserve">P2</t>
-        </is>
-      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K219"/>
+  <autoFilter ref="A1:K197"/>
 </worksheet>
 </file>
 
